--- a/data/seat/10-octubre 2026.xlsx
+++ b/data/seat/10-octubre 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Datos/Energía/SEAT/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{F61CAED6-267A-4B2C-80CD-4BC72F22561D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB74727D-D8CC-4B91-9EC1-23213C173EE6}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="14_{F61CAED6-267A-4B2C-80CD-4BC72F22561D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D4DD74E-FF8E-4739-B864-54E8A95EAB7E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEAT-SERs" sheetId="1" r:id="rId1"/>
@@ -365,7 +365,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="70">
   <si>
     <t>Fecha</t>
   </si>
@@ -572,6 +572,9 @@
   </si>
   <si>
     <t>DDA Max 12 Kva</t>
+  </si>
+  <si>
+    <t>11.45</t>
   </si>
 </sst>
 </file>
@@ -1608,7 +1611,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2056,59 +2059,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2140,6 +2092,39 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2152,10 +2137,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2233,7 +2239,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2257,7 +2266,77 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="97">
+  <dxfs count="107">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4174,52 +4253,52 @@
                   <c:v>2389</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>2904.36</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>2937.7299999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>2988.58</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>2872</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>2567</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>2482</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>2968</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>2887</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>2763.23</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>2849.67</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>2748</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>2413</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>2446</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>2918.5800000000004</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0</c:v>
+                  <c:v>2975.02</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>2946</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -7119,293 +7198,293 @@
       <c r="A1" s="124">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="184" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="125"/>
-      <c r="D1" s="203" t="s">
+      <c r="D1" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="204"/>
-      <c r="O1" s="205"/>
-      <c r="P1" s="206"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
+      <c r="L1" s="187"/>
+      <c r="M1" s="187"/>
+      <c r="N1" s="187"/>
+      <c r="O1" s="188"/>
+      <c r="P1" s="189"/>
       <c r="Q1" s="126"/>
-      <c r="R1" s="183" t="s">
+      <c r="R1" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="184"/>
-      <c r="T1" s="184"/>
-      <c r="U1" s="184"/>
-      <c r="V1" s="184"/>
-      <c r="W1" s="184"/>
-      <c r="X1" s="184"/>
-      <c r="Y1" s="184"/>
-      <c r="Z1" s="184"/>
-      <c r="AA1" s="185"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
+      <c r="X1" s="195"/>
+      <c r="Y1" s="195"/>
+      <c r="Z1" s="195"/>
+      <c r="AA1" s="196"/>
       <c r="AB1" s="127"/>
-      <c r="AC1" s="183" t="s">
+      <c r="AC1" s="194" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="184"/>
-      <c r="AE1" s="184"/>
-      <c r="AF1" s="184"/>
-      <c r="AG1" s="184"/>
-      <c r="AH1" s="184"/>
-      <c r="AI1" s="184"/>
-      <c r="AJ1" s="184"/>
-      <c r="AK1" s="185"/>
+      <c r="AD1" s="195"/>
+      <c r="AE1" s="195"/>
+      <c r="AF1" s="195"/>
+      <c r="AG1" s="195"/>
+      <c r="AH1" s="195"/>
+      <c r="AI1" s="195"/>
+      <c r="AJ1" s="195"/>
+      <c r="AK1" s="196"/>
       <c r="AL1" s="128"/>
-      <c r="AM1" s="183" t="s">
+      <c r="AM1" s="194" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="184"/>
-      <c r="AO1" s="184"/>
-      <c r="AP1" s="184"/>
-      <c r="AQ1" s="184"/>
-      <c r="AR1" s="184"/>
-      <c r="AS1" s="184"/>
-      <c r="AT1" s="184"/>
-      <c r="AU1" s="185"/>
+      <c r="AN1" s="195"/>
+      <c r="AO1" s="195"/>
+      <c r="AP1" s="195"/>
+      <c r="AQ1" s="195"/>
+      <c r="AR1" s="195"/>
+      <c r="AS1" s="195"/>
+      <c r="AT1" s="195"/>
+      <c r="AU1" s="196"/>
       <c r="AV1" s="128"/>
-      <c r="AW1" s="183" t="s">
+      <c r="AW1" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="184"/>
-      <c r="AY1" s="184"/>
-      <c r="AZ1" s="184"/>
-      <c r="BA1" s="184"/>
-      <c r="BB1" s="184"/>
-      <c r="BC1" s="184"/>
-      <c r="BD1" s="184"/>
-      <c r="BE1" s="184"/>
-      <c r="BF1" s="184"/>
-      <c r="BG1" s="184"/>
-      <c r="BH1" s="185"/>
+      <c r="AX1" s="195"/>
+      <c r="AY1" s="195"/>
+      <c r="AZ1" s="195"/>
+      <c r="BA1" s="195"/>
+      <c r="BB1" s="195"/>
+      <c r="BC1" s="195"/>
+      <c r="BD1" s="195"/>
+      <c r="BE1" s="195"/>
+      <c r="BF1" s="195"/>
+      <c r="BG1" s="195"/>
+      <c r="BH1" s="196"/>
       <c r="BI1" s="128"/>
-      <c r="BJ1" s="183" t="s">
+      <c r="BJ1" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="184"/>
-      <c r="BL1" s="184"/>
-      <c r="BM1" s="184"/>
-      <c r="BN1" s="184"/>
-      <c r="BO1" s="184"/>
-      <c r="BP1" s="184"/>
-      <c r="BQ1" s="184"/>
-      <c r="BR1" s="185"/>
+      <c r="BK1" s="195"/>
+      <c r="BL1" s="195"/>
+      <c r="BM1" s="195"/>
+      <c r="BN1" s="195"/>
+      <c r="BO1" s="195"/>
+      <c r="BP1" s="195"/>
+      <c r="BQ1" s="195"/>
+      <c r="BR1" s="196"/>
       <c r="BS1" s="129"/>
     </row>
     <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="201"/>
+      <c r="B2" s="184"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
-      <c r="M2" s="208"/>
-      <c r="N2" s="208"/>
-      <c r="O2" s="209"/>
-      <c r="P2" s="210"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="191"/>
+      <c r="N2" s="191"/>
+      <c r="O2" s="192"/>
+      <c r="P2" s="193"/>
       <c r="Q2" s="56"/>
-      <c r="R2" s="186"/>
-      <c r="S2" s="187"/>
-      <c r="T2" s="187"/>
-      <c r="U2" s="187"/>
-      <c r="V2" s="187"/>
-      <c r="W2" s="187"/>
-      <c r="X2" s="187"/>
-      <c r="Y2" s="187"/>
-      <c r="Z2" s="187"/>
-      <c r="AA2" s="188"/>
+      <c r="R2" s="197"/>
+      <c r="S2" s="198"/>
+      <c r="T2" s="198"/>
+      <c r="U2" s="198"/>
+      <c r="V2" s="198"/>
+      <c r="W2" s="198"/>
+      <c r="X2" s="198"/>
+      <c r="Y2" s="198"/>
+      <c r="Z2" s="198"/>
+      <c r="AA2" s="199"/>
       <c r="AB2" s="58"/>
-      <c r="AC2" s="186"/>
-      <c r="AD2" s="187"/>
-      <c r="AE2" s="187"/>
-      <c r="AF2" s="187"/>
-      <c r="AG2" s="187"/>
-      <c r="AH2" s="187"/>
-      <c r="AI2" s="187"/>
-      <c r="AJ2" s="187"/>
-      <c r="AK2" s="188"/>
+      <c r="AC2" s="197"/>
+      <c r="AD2" s="198"/>
+      <c r="AE2" s="198"/>
+      <c r="AF2" s="198"/>
+      <c r="AG2" s="198"/>
+      <c r="AH2" s="198"/>
+      <c r="AI2" s="198"/>
+      <c r="AJ2" s="198"/>
+      <c r="AK2" s="199"/>
       <c r="AL2" s="57"/>
-      <c r="AM2" s="186"/>
-      <c r="AN2" s="187"/>
-      <c r="AO2" s="187"/>
-      <c r="AP2" s="187"/>
-      <c r="AQ2" s="187"/>
-      <c r="AR2" s="187"/>
-      <c r="AS2" s="187"/>
-      <c r="AT2" s="187"/>
-      <c r="AU2" s="188"/>
+      <c r="AM2" s="197"/>
+      <c r="AN2" s="198"/>
+      <c r="AO2" s="198"/>
+      <c r="AP2" s="198"/>
+      <c r="AQ2" s="198"/>
+      <c r="AR2" s="198"/>
+      <c r="AS2" s="198"/>
+      <c r="AT2" s="198"/>
+      <c r="AU2" s="199"/>
       <c r="AV2" s="57"/>
-      <c r="AW2" s="186"/>
-      <c r="AX2" s="187"/>
-      <c r="AY2" s="187"/>
-      <c r="AZ2" s="187"/>
-      <c r="BA2" s="187"/>
-      <c r="BB2" s="187"/>
-      <c r="BC2" s="187"/>
-      <c r="BD2" s="187"/>
-      <c r="BE2" s="187"/>
-      <c r="BF2" s="187"/>
-      <c r="BG2" s="187"/>
-      <c r="BH2" s="188"/>
+      <c r="AW2" s="197"/>
+      <c r="AX2" s="198"/>
+      <c r="AY2" s="198"/>
+      <c r="AZ2" s="198"/>
+      <c r="BA2" s="198"/>
+      <c r="BB2" s="198"/>
+      <c r="BC2" s="198"/>
+      <c r="BD2" s="198"/>
+      <c r="BE2" s="198"/>
+      <c r="BF2" s="198"/>
+      <c r="BG2" s="198"/>
+      <c r="BH2" s="199"/>
       <c r="BI2" s="57"/>
-      <c r="BJ2" s="186"/>
-      <c r="BK2" s="187"/>
-      <c r="BL2" s="187"/>
-      <c r="BM2" s="187"/>
-      <c r="BN2" s="187"/>
-      <c r="BO2" s="187"/>
-      <c r="BP2" s="187"/>
-      <c r="BQ2" s="187"/>
-      <c r="BR2" s="188"/>
+      <c r="BJ2" s="197"/>
+      <c r="BK2" s="198"/>
+      <c r="BL2" s="198"/>
+      <c r="BM2" s="198"/>
+      <c r="BN2" s="198"/>
+      <c r="BO2" s="198"/>
+      <c r="BP2" s="198"/>
+      <c r="BQ2" s="198"/>
+      <c r="BR2" s="199"/>
       <c r="BS2" s="132"/>
     </row>
     <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="201"/>
+      <c r="B3" s="184"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="189" t="s">
+      <c r="D3" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="189" t="s">
+      <c r="E3" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="189" t="s">
+      <c r="F3" s="203" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="189" t="s">
+      <c r="G3" s="203" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="189" t="s">
+      <c r="H3" s="203" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="211" t="s">
+      <c r="I3" s="205" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="212"/>
-      <c r="K3" s="213"/>
-      <c r="L3" s="214"/>
-      <c r="M3" s="211" t="s">
+      <c r="J3" s="206"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="208"/>
+      <c r="M3" s="205" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="212"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="214"/>
+      <c r="N3" s="206"/>
+      <c r="O3" s="207"/>
+      <c r="P3" s="208"/>
       <c r="Q3" s="56"/>
-      <c r="R3" s="193" t="s">
+      <c r="R3" s="209" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="194"/>
-      <c r="T3" s="215"/>
-      <c r="U3" s="215"/>
-      <c r="V3" s="193" t="s">
+      <c r="S3" s="201"/>
+      <c r="T3" s="210"/>
+      <c r="U3" s="210"/>
+      <c r="V3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="194"/>
-      <c r="X3" s="194"/>
-      <c r="Y3" s="194"/>
-      <c r="Z3" s="194"/>
-      <c r="AA3" s="195"/>
+      <c r="W3" s="201"/>
+      <c r="X3" s="201"/>
+      <c r="Y3" s="201"/>
+      <c r="Z3" s="201"/>
+      <c r="AA3" s="202"/>
       <c r="AB3" s="58"/>
-      <c r="AC3" s="191" t="s">
+      <c r="AC3" s="211" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="216" t="s">
+      <c r="AD3" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="193" t="s">
+      <c r="AE3" s="209" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="194"/>
-      <c r="AG3" s="195"/>
-      <c r="AH3" s="193" t="s">
+      <c r="AF3" s="201"/>
+      <c r="AG3" s="202"/>
+      <c r="AH3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="194"/>
-      <c r="AJ3" s="194"/>
-      <c r="AK3" s="195"/>
+      <c r="AI3" s="201"/>
+      <c r="AJ3" s="201"/>
+      <c r="AK3" s="202"/>
       <c r="AL3" s="57"/>
-      <c r="AM3" s="196" t="s">
+      <c r="AM3" s="214" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="191" t="s">
+      <c r="AN3" s="211" t="s">
         <v>9</v>
       </c>
       <c r="AO3" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="194"/>
-      <c r="AQ3" s="195"/>
-      <c r="AR3" s="193" t="s">
+      <c r="AP3" s="201"/>
+      <c r="AQ3" s="202"/>
+      <c r="AR3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="194"/>
-      <c r="AT3" s="194"/>
-      <c r="AU3" s="195"/>
+      <c r="AS3" s="201"/>
+      <c r="AT3" s="201"/>
+      <c r="AU3" s="202"/>
       <c r="AV3" s="57"/>
-      <c r="AW3" s="191" t="s">
+      <c r="AW3" s="211" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="191" t="s">
+      <c r="AX3" s="211" t="s">
         <v>9</v>
       </c>
       <c r="AY3" s="200" t="s">
         <v>13</v>
       </c>
       <c r="AZ3" s="200"/>
-      <c r="BA3" s="194"/>
-      <c r="BB3" s="195"/>
-      <c r="BC3" s="193" t="s">
+      <c r="BA3" s="201"/>
+      <c r="BB3" s="202"/>
+      <c r="BC3" s="209" t="s">
         <v>14</v>
       </c>
       <c r="BD3" s="200"/>
       <c r="BE3" s="200"/>
-      <c r="BF3" s="194"/>
-      <c r="BG3" s="194"/>
-      <c r="BH3" s="195"/>
+      <c r="BF3" s="201"/>
+      <c r="BG3" s="201"/>
+      <c r="BH3" s="202"/>
       <c r="BI3" s="57"/>
-      <c r="BJ3" s="196" t="s">
+      <c r="BJ3" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="191" t="s">
+      <c r="BK3" s="211" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="197" t="s">
+      <c r="BL3" s="215" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="198"/>
-      <c r="BN3" s="199"/>
+      <c r="BM3" s="216"/>
+      <c r="BN3" s="217"/>
       <c r="BO3" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="194"/>
-      <c r="BQ3" s="194"/>
-      <c r="BR3" s="195"/>
+      <c r="BP3" s="201"/>
+      <c r="BQ3" s="201"/>
+      <c r="BR3" s="202"/>
       <c r="BS3" s="132"/>
     </row>
     <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="202"/>
+      <c r="B4" s="185"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="204"/>
       <c r="I4" s="78" t="s">
         <v>3</v>
       </c>
@@ -7462,8 +7541,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="58"/>
-      <c r="AC4" s="192"/>
-      <c r="AD4" s="184"/>
+      <c r="AC4" s="212"/>
+      <c r="AD4" s="195"/>
       <c r="AE4" s="60" t="s">
         <v>27</v>
       </c>
@@ -7486,8 +7565,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="59"/>
-      <c r="AM4" s="183"/>
-      <c r="AN4" s="192"/>
+      <c r="AM4" s="194"/>
+      <c r="AN4" s="212"/>
       <c r="AO4" s="120" t="s">
         <v>27</v>
       </c>
@@ -7510,8 +7589,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="59"/>
-      <c r="AW4" s="192"/>
-      <c r="AX4" s="192"/>
+      <c r="AW4" s="212"/>
+      <c r="AX4" s="212"/>
       <c r="AY4" s="120" t="s">
         <v>27</v>
       </c>
@@ -7543,8 +7622,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="59"/>
-      <c r="BJ4" s="183"/>
-      <c r="BK4" s="192"/>
+      <c r="BJ4" s="194"/>
+      <c r="BK4" s="212"/>
       <c r="BL4" s="120" t="s">
         <v>32</v>
       </c>
@@ -10923,7 +11002,7 @@
       <c r="AZ19" s="109">
         <v>10148.5</v>
       </c>
-      <c r="BA19" s="242">
+      <c r="BA19" s="183">
         <f t="shared" si="15"/>
         <v>6731.1275000000005</v>
       </c>
@@ -11162,7 +11241,7 @@
       <c r="AZ20" s="109">
         <v>10201</v>
       </c>
-      <c r="BA20" s="242">
+      <c r="BA20" s="183">
         <f t="shared" si="15"/>
         <v>6843.7474999999995</v>
       </c>
@@ -11402,7 +11481,7 @@
       <c r="AZ21" s="109">
         <v>10140</v>
       </c>
-      <c r="BA21" s="242">
+      <c r="BA21" s="183">
         <f t="shared" si="15"/>
         <v>6719.7474999999995</v>
       </c>
@@ -11642,7 +11721,7 @@
       <c r="AZ22" s="109">
         <v>10380</v>
       </c>
-      <c r="BA22" s="242">
+      <c r="BA22" s="183">
         <f t="shared" si="15"/>
         <v>6985.3775000000005</v>
       </c>
@@ -11882,7 +11961,7 @@
       <c r="AZ23" s="109">
         <v>5081</v>
       </c>
-      <c r="BA23" s="242">
+      <c r="BA23" s="183">
         <f t="shared" si="15"/>
         <v>1730.3775000000001</v>
       </c>
@@ -12122,7 +12201,7 @@
       <c r="AZ24" s="109">
         <v>4629</v>
       </c>
-      <c r="BA24" s="242">
+      <c r="BA24" s="183">
         <f t="shared" si="15"/>
         <v>1287.3775000000001</v>
       </c>
@@ -12362,7 +12441,7 @@
       <c r="AZ25" s="109">
         <v>10231</v>
       </c>
-      <c r="BA25" s="242">
+      <c r="BA25" s="183">
         <f t="shared" si="15"/>
         <v>6764.3775000000005</v>
       </c>
@@ -12602,7 +12681,7 @@
       <c r="AZ26" s="109">
         <v>9376</v>
       </c>
-      <c r="BA26" s="242">
+      <c r="BA26" s="183">
         <f t="shared" si="15"/>
         <v>5855.3775000000005</v>
       </c>
@@ -12842,7 +12921,7 @@
       <c r="AZ27" s="109">
         <v>10281</v>
       </c>
-      <c r="BA27" s="242">
+      <c r="BA27" s="183">
         <f t="shared" si="15"/>
         <v>6836.0774999999994</v>
       </c>
@@ -13082,7 +13161,7 @@
       <c r="AZ28" s="109">
         <v>10576</v>
       </c>
-      <c r="BA28" s="242">
+      <c r="BA28" s="183">
         <f t="shared" si="15"/>
         <v>7110.6275000000005</v>
       </c>
@@ -13322,7 +13401,7 @@
       <c r="AZ29" s="109">
         <v>10539</v>
       </c>
-      <c r="BA29" s="242">
+      <c r="BA29" s="183">
         <f t="shared" si="15"/>
         <v>7233.3775000000005</v>
       </c>
@@ -13562,7 +13641,7 @@
       <c r="AZ30" s="109">
         <v>4297</v>
       </c>
-      <c r="BA30" s="242">
+      <c r="BA30" s="183">
         <f t="shared" si="15"/>
         <v>1470.3775000000001</v>
       </c>
@@ -13802,7 +13881,7 @@
       <c r="AZ31" s="109">
         <v>4607</v>
       </c>
-      <c r="BA31" s="242">
+      <c r="BA31" s="183">
         <f t="shared" si="15"/>
         <v>1137.3775000000001</v>
       </c>
@@ -13875,19 +13954,19 @@
       </c>
       <c r="E32" s="156">
         <f t="shared" si="0"/>
-        <v>0.88251214820813928</v>
+        <v>0.87222628568536142</v>
       </c>
       <c r="F32" s="85">
         <f t="shared" si="1"/>
-        <v>52304.729999999996</v>
+        <v>51695.107499999998</v>
       </c>
       <c r="G32" s="156">
         <f t="shared" si="2"/>
-        <v>0.11748785179186071</v>
+        <v>0.1277737143146386</v>
       </c>
       <c r="H32" s="143">
         <f t="shared" si="3"/>
-        <v>6963.27</v>
+        <v>7572.8924999999999</v>
       </c>
       <c r="I32" s="157">
         <f t="shared" si="4"/>
@@ -14029,11 +14108,11 @@
       </c>
       <c r="AW32" s="166">
         <f t="shared" si="47"/>
-        <v>0.69974024691358028</v>
+        <v>0.63953061728395055</v>
       </c>
       <c r="AX32" s="166">
         <f t="shared" si="48"/>
-        <v>0.30025975308641978</v>
+        <v>0.36046938271604939</v>
       </c>
       <c r="AY32" s="108">
         <f t="shared" si="26"/>
@@ -14042,12 +14121,13 @@
       <c r="AZ32" s="109">
         <v>10125</v>
       </c>
-      <c r="BA32" s="242">
+      <c r="BA32" s="183">
         <f t="shared" si="15"/>
-        <v>7084.87</v>
+        <v>6475.2474999999995</v>
       </c>
       <c r="BB32" s="110">
-        <v>3040.13</v>
+        <f>3040.13+BB39</f>
+        <v>3649.7525000000001</v>
       </c>
       <c r="BC32" s="109">
         <v>4496.71</v>
@@ -14110,164 +14190,209 @@
       <c r="C33" s="161"/>
       <c r="D33" s="85">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="156" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>64292</v>
+      </c>
+      <c r="E33" s="156">
+        <v>0.89097430473464823</v>
       </c>
       <c r="F33" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="156" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>56672.897499999999</v>
+      </c>
+      <c r="G33" s="156">
+        <v>0.10902569526535183</v>
       </c>
       <c r="H33" s="143">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="157" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J33" s="156" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K33" s="156" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L33" s="158" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M33" s="143" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N33" s="143" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O33" s="143" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P33" s="143" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>7619.1025</v>
+      </c>
+      <c r="I33" s="157">
+        <v>0.11673365736771101</v>
+      </c>
+      <c r="J33" s="156">
+        <v>0.15356644166688699</v>
+      </c>
+      <c r="K33" s="156">
+        <v>0.17523340066317916</v>
+      </c>
+      <c r="L33" s="158">
+        <v>0.57723782307431981</v>
+      </c>
+      <c r="M33" s="143">
+        <v>7422.4372288583363</v>
+      </c>
+      <c r="N33" s="143">
+        <v>9764.4269821951748</v>
+      </c>
+      <c r="O33" s="143">
+        <v>11142.107136459836</v>
+      </c>
+      <c r="P33" s="143">
+        <v>36703.30909273032</v>
       </c>
       <c r="Q33" s="54">
-        <f t="shared" si="38"/>
         <v>46322</v>
       </c>
-      <c r="R33" s="136"/>
-      <c r="S33" s="137"/>
-      <c r="T33" s="137"/>
-      <c r="U33" s="137"/>
-      <c r="V33" s="138"/>
-      <c r="W33" s="139"/>
-      <c r="X33" s="138"/>
-      <c r="Y33" s="139"/>
-      <c r="Z33" s="138"/>
-      <c r="AA33" s="139"/>
+      <c r="R33" s="136">
+        <v>64292</v>
+      </c>
+      <c r="S33" s="137">
+        <v>63584.38</v>
+      </c>
+      <c r="T33" s="137">
+        <v>0</v>
+      </c>
+      <c r="U33" s="137">
+        <v>0</v>
+      </c>
+      <c r="V33" s="138">
+        <v>14841.08</v>
+      </c>
+      <c r="W33" s="139">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="X33" s="138">
+        <v>5206.54</v>
+      </c>
+      <c r="Y33" s="139">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="Z33" s="138">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="139">
+        <v>0</v>
+      </c>
       <c r="AB33" s="54">
-        <f t="shared" si="39"/>
         <v>46322</v>
       </c>
-      <c r="AC33" s="74" t="e">
-        <f t="shared" ref="AC26:AC36" si="51">+AF33/AE33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD33" s="159" t="e">
-        <f t="shared" ref="AD26:AD36" si="52">+AG33/AE33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE33" s="160"/>
+      <c r="AC33" s="74">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="159">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="160">
+        <v>8344.1299999999992</v>
+      </c>
       <c r="AF33" s="115">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AG33" s="144"/>
-      <c r="AH33" s="145"/>
-      <c r="AI33" s="146"/>
-      <c r="AJ33" s="145"/>
-      <c r="AK33" s="162"/>
+        <v>8344.1299999999992</v>
+      </c>
+      <c r="AG33" s="144">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="145">
+        <v>3853.24</v>
+      </c>
+      <c r="AI33" s="146">
+        <v>0.68194444444444446</v>
+      </c>
+      <c r="AJ33" s="145">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="162">
+        <v>0</v>
+      </c>
       <c r="AL33" s="165">
-        <f t="shared" si="40"/>
         <v>46322</v>
       </c>
-      <c r="AM33" s="75" t="e">
-        <f t="shared" ref="AM26:AM36" si="53">+AP33/AO33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN33" s="74" t="e">
-        <f t="shared" ref="AN26:AN36" si="54">+AQ33/AO33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO33" s="147"/>
+      <c r="AM33" s="75">
+        <v>0.63958717092377293</v>
+      </c>
+      <c r="AN33" s="74">
+        <v>0.36041282907622707</v>
+      </c>
+      <c r="AO33" s="147">
+        <v>10976.94</v>
+      </c>
       <c r="AP33" s="114">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AQ33" s="148"/>
-      <c r="AR33" s="149"/>
-      <c r="AS33" s="150"/>
-      <c r="AT33" s="149"/>
-      <c r="AU33" s="151"/>
+        <v>7020.7100000000009</v>
+      </c>
+      <c r="AQ33" s="148">
+        <v>3956.23</v>
+      </c>
+      <c r="AR33" s="149">
+        <v>3668.73</v>
+      </c>
+      <c r="AS33" s="150">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="AT33" s="149">
+        <v>193.48</v>
+      </c>
+      <c r="AU33" s="151">
+        <v>0.84375</v>
+      </c>
       <c r="AV33" s="54">
-        <f t="shared" si="41"/>
         <v>46322</v>
       </c>
-      <c r="AW33" s="166" t="e">
-        <f t="shared" ref="AW26:AW36" si="55">BA33/AZ33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX33" s="166" t="e">
-        <f t="shared" ref="AX26:AX36" si="56">BB33/AZ33</f>
-        <v>#DIV/0!</v>
+      <c r="AW33" s="166">
+        <v>0.719833914479721</v>
+      </c>
+      <c r="AX33" s="166">
+        <v>0.28016608552027894</v>
       </c>
       <c r="AY33" s="108">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AZ33" s="109"/>
+        <v>10898</v>
+      </c>
+      <c r="AZ33" s="109">
+        <v>10898</v>
+      </c>
       <c r="BA33" s="117">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BB33" s="110"/>
-      <c r="BC33" s="109"/>
-      <c r="BD33" s="111"/>
-      <c r="BE33" s="112"/>
-      <c r="BF33" s="111"/>
-      <c r="BG33" s="112"/>
-      <c r="BH33" s="111"/>
+        <v>7844.75</v>
+      </c>
+      <c r="BB33" s="110">
+        <f>3053.25+BB39</f>
+        <v>3662.8724999999999</v>
+      </c>
+      <c r="BC33" s="109">
+        <v>4535.9399999999996</v>
+      </c>
+      <c r="BD33" s="111">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="BE33" s="112">
+        <v>0</v>
+      </c>
+      <c r="BF33" s="111">
+        <v>0</v>
+      </c>
+      <c r="BG33" s="112">
+        <v>182.23</v>
+      </c>
+      <c r="BH33" s="111">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="BI33" s="54">
-        <f t="shared" si="42"/>
         <v>46322</v>
       </c>
-      <c r="BJ33" s="167" t="e">
-        <f t="shared" ref="BJ26:BJ36" si="57">+BM33/BL33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK33" s="74" t="e">
-        <f t="shared" ref="BK26:BK36" si="58">+BN33/BL33</f>
-        <v>#DIV/0!</v>
+      <c r="BJ33" s="167">
+        <v>0.60663822980538518</v>
+      </c>
+      <c r="BK33" s="74">
+        <v>0.39336177019461477</v>
       </c>
       <c r="BL33" s="77">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BM33" s="152"/>
-      <c r="BN33" s="152"/>
-      <c r="BO33" s="153"/>
-      <c r="BP33" s="154"/>
-      <c r="BQ33" s="155"/>
-      <c r="BR33" s="154"/>
+        <v>41261</v>
+      </c>
+      <c r="BM33" s="152">
+        <v>25030.5</v>
+      </c>
+      <c r="BN33" s="152">
+        <v>16230.5</v>
+      </c>
+      <c r="BO33" s="153">
+        <v>4727.46</v>
+      </c>
+      <c r="BP33" s="154">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="BQ33" s="155">
+        <v>3156.55</v>
+      </c>
+      <c r="BR33" s="154">
+        <v>0.36527777777777776</v>
+      </c>
     </row>
     <row r="34" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14"/>
@@ -14277,164 +14402,209 @@
       <c r="C34" s="161"/>
       <c r="D34" s="85">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="E34" s="156" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>63340</v>
+      </c>
+      <c r="E34" s="156">
+        <v>0.8887432901799811</v>
       </c>
       <c r="F34" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="156" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>55683.377500000002</v>
+      </c>
+      <c r="G34" s="156">
+        <v>0.11125670982001895</v>
       </c>
       <c r="H34" s="143">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="157" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J34" s="156" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K34" s="156" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L34" s="158" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M34" s="143" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N34" s="143" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O34" s="143" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P34" s="143" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>7656.6224999999995</v>
+      </c>
+      <c r="I34" s="157">
+        <v>0.12199775053745071</v>
+      </c>
+      <c r="J34" s="156">
+        <v>0.16431042583180283</v>
+      </c>
+      <c r="K34" s="156">
+        <v>0.17488065950895257</v>
+      </c>
+      <c r="L34" s="158">
+        <v>0.56087074132604398</v>
+      </c>
+      <c r="M34" s="143">
+        <v>7641.8170959153749</v>
+      </c>
+      <c r="N34" s="143">
+        <v>10292.240763678297</v>
+      </c>
+      <c r="O34" s="143">
+        <v>10954.34963098128</v>
+      </c>
+      <c r="P34" s="143">
+        <v>35132.382365922065</v>
       </c>
       <c r="Q34" s="54">
-        <f t="shared" si="38"/>
         <v>46323</v>
       </c>
-      <c r="R34" s="136"/>
-      <c r="S34" s="137"/>
-      <c r="T34" s="137"/>
-      <c r="U34" s="137"/>
-      <c r="V34" s="138"/>
-      <c r="W34" s="139"/>
-      <c r="X34" s="138"/>
-      <c r="Y34" s="139"/>
-      <c r="Z34" s="138"/>
-      <c r="AA34" s="139"/>
+      <c r="R34" s="136">
+        <v>63340</v>
+      </c>
+      <c r="S34" s="137">
+        <v>62639</v>
+      </c>
+      <c r="T34" s="137">
+        <v>0</v>
+      </c>
+      <c r="U34" s="137">
+        <v>0</v>
+      </c>
+      <c r="V34" s="138">
+        <v>16249</v>
+      </c>
+      <c r="W34" s="139">
+        <v>0.40625</v>
+      </c>
+      <c r="X34" s="138">
+        <v>5275</v>
+      </c>
+      <c r="Y34" s="139">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="Z34" s="138">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="139">
+        <v>0</v>
+      </c>
       <c r="AB34" s="54">
-        <f t="shared" si="39"/>
         <v>46323</v>
       </c>
-      <c r="AC34" s="74" t="e">
-        <f t="shared" si="51"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD34" s="159" t="e">
-        <f t="shared" si="52"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE34" s="160"/>
+      <c r="AC34" s="74">
+        <v>1</v>
+      </c>
+      <c r="AD34" s="159">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="160">
+        <v>8569</v>
+      </c>
       <c r="AF34" s="115">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AG34" s="144"/>
-      <c r="AH34" s="145"/>
-      <c r="AI34" s="146"/>
-      <c r="AJ34" s="145"/>
-      <c r="AK34" s="162"/>
+        <v>8569</v>
+      </c>
+      <c r="AG34" s="144">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="145">
+        <v>3935</v>
+      </c>
+      <c r="AI34" s="146">
+        <v>0.33055555555555555</v>
+      </c>
+      <c r="AJ34" s="145">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="162">
+        <v>0</v>
+      </c>
       <c r="AL34" s="54">
-        <f t="shared" si="40"/>
         <v>46323</v>
       </c>
-      <c r="AM34" s="75" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN34" s="74" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO34" s="147"/>
+      <c r="AM34" s="75">
+        <v>0.65427605926696131</v>
+      </c>
+      <c r="AN34" s="74">
+        <v>0.34572394073303875</v>
+      </c>
+      <c r="AO34" s="147">
+        <v>11541</v>
+      </c>
       <c r="AP34" s="114">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="148"/>
-      <c r="AR34" s="149"/>
-      <c r="AS34" s="150"/>
-      <c r="AT34" s="149"/>
-      <c r="AU34" s="151"/>
+        <v>7551</v>
+      </c>
+      <c r="AQ34" s="148">
+        <v>3990</v>
+      </c>
+      <c r="AR34" s="149">
+        <v>4816</v>
+      </c>
+      <c r="AS34" s="150">
+        <v>0.36527777777777776</v>
+      </c>
+      <c r="AT34" s="149">
+        <v>184</v>
+      </c>
+      <c r="AU34" s="151">
+        <v>0.88541666666666663</v>
+      </c>
       <c r="AV34" s="54">
-        <f t="shared" si="41"/>
         <v>46323</v>
       </c>
-      <c r="AW34" s="107" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX34" s="107" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
+      <c r="AW34" s="107">
+        <v>0.71520402459474564</v>
+      </c>
+      <c r="AX34" s="107">
+        <v>0.28479597540525431</v>
       </c>
       <c r="AY34" s="108">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AZ34" s="109"/>
+        <v>10734</v>
+      </c>
+      <c r="AZ34" s="109">
+        <v>10734</v>
+      </c>
       <c r="BA34" s="117">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BB34" s="110"/>
-      <c r="BC34" s="109"/>
-      <c r="BD34" s="111"/>
-      <c r="BE34" s="112"/>
-      <c r="BF34" s="111"/>
-      <c r="BG34" s="112"/>
-      <c r="BH34" s="111"/>
+        <v>7677</v>
+      </c>
+      <c r="BB34" s="110">
+        <f>3057+BB39</f>
+        <v>3666.6224999999999</v>
+      </c>
+      <c r="BC34" s="109">
+        <v>4963</v>
+      </c>
+      <c r="BD34" s="111">
+        <v>0.71875</v>
+      </c>
+      <c r="BE34" s="112">
+        <v>0</v>
+      </c>
+      <c r="BF34" s="111">
+        <v>0</v>
+      </c>
+      <c r="BG34" s="112">
+        <v>175</v>
+      </c>
+      <c r="BH34" s="111">
+        <v>0.875</v>
+      </c>
       <c r="BI34" s="54">
-        <f t="shared" si="42"/>
         <v>46323</v>
       </c>
-      <c r="BJ34" s="76" t="e">
-        <f t="shared" si="57"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK34" s="74" t="e">
-        <f t="shared" si="58"/>
-        <v>#DIV/0!</v>
+      <c r="BJ34" s="76">
+        <v>0.60390912552354359</v>
+      </c>
+      <c r="BK34" s="74">
+        <v>0.39609087447645641</v>
       </c>
       <c r="BL34" s="77">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BM34" s="152"/>
-      <c r="BN34" s="152"/>
-      <c r="BO34" s="153"/>
-      <c r="BP34" s="154"/>
-      <c r="BQ34" s="155"/>
-      <c r="BR34" s="154"/>
+        <v>39395</v>
+      </c>
+      <c r="BM34" s="152">
+        <v>23791</v>
+      </c>
+      <c r="BN34" s="152">
+        <v>15604</v>
+      </c>
+      <c r="BO34" s="153">
+        <v>4574</v>
+      </c>
+      <c r="BP34" s="154">
+        <v>0.71111111111111114</v>
+      </c>
+      <c r="BQ34" s="155">
+        <v>3038</v>
+      </c>
+      <c r="BR34" s="154">
+        <v>0.71111111111111114</v>
+      </c>
     </row>
     <row r="35" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14"/>
@@ -14513,11 +14683,11 @@
         <v>46324</v>
       </c>
       <c r="AC35" s="74" t="e">
-        <f t="shared" ref="AC35" si="59">+AF35/AE35</f>
+        <f t="shared" ref="AC35" si="51">+AF35/AE35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD35" s="159" t="e">
-        <f t="shared" ref="AD35" si="60">+AG35/AE35</f>
+        <f t="shared" ref="AD35" si="52">+AG35/AE35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE35" s="160"/>
@@ -14535,11 +14705,11 @@
         <v>46324</v>
       </c>
       <c r="AM35" s="75" t="e">
-        <f t="shared" ref="AM35" si="61">+AP35/AO35</f>
+        <f t="shared" ref="AM35" si="53">+AP35/AO35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN35" s="74" t="e">
-        <f t="shared" ref="AN35" si="62">+AQ35/AO35</f>
+        <f t="shared" ref="AN35" si="54">+AQ35/AO35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AO35" s="147"/>
@@ -14557,11 +14727,11 @@
         <v>46324</v>
       </c>
       <c r="AW35" s="107" t="e">
-        <f t="shared" ref="AW35" si="63">BA35/AZ35</f>
+        <f t="shared" ref="AW35" si="55">BA35/AZ35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX35" s="107" t="e">
-        <f t="shared" ref="AX35" si="64">BB35/AZ35</f>
+        <f t="shared" ref="AX35" si="56">BB35/AZ35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AY35" s="108">
@@ -14585,11 +14755,11 @@
         <v>46324</v>
       </c>
       <c r="BJ35" s="76" t="e">
-        <f t="shared" ref="BJ35" si="65">+BM35/BL35</f>
+        <f t="shared" ref="BJ35" si="57">+BM35/BL35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BK35" s="74" t="e">
-        <f t="shared" ref="BK35" si="66">+BN35/BL35</f>
+        <f t="shared" ref="BK35" si="58">+BN35/BL35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BL35" s="77">
@@ -14614,7 +14784,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="156" t="e">
-        <f t="shared" ref="E36:E37" si="67">F36/D36</f>
+        <f t="shared" ref="E36:E37" si="59">F36/D36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F36" s="85">
@@ -14680,11 +14850,11 @@
         <v>46325</v>
       </c>
       <c r="AC36" s="74" t="e">
-        <f t="shared" si="51"/>
+        <f t="shared" ref="AC36" si="60">+AF36/AE36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD36" s="159" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="AD36" si="61">+AG36/AE36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE36" s="160"/>
@@ -14702,11 +14872,11 @@
         <v>46325</v>
       </c>
       <c r="AM36" s="75" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="AM36" si="62">+AP36/AO36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN36" s="74" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="AN36" si="63">+AQ36/AO36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AO36" s="147"/>
@@ -14724,11 +14894,11 @@
         <v>46325</v>
       </c>
       <c r="AW36" s="107" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="AW36" si="64">BA36/AZ36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX36" s="107" t="e">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="AX36" si="65">BB36/AZ36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AY36" s="108">
@@ -14752,11 +14922,11 @@
         <v>46325</v>
       </c>
       <c r="BJ36" s="76" t="e">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="BJ36" si="66">+BM36/BL36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BK36" s="74" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="BK36" si="67">+BN36/BL36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BL36" s="77">
@@ -14779,7 +14949,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="156" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F37" s="85">
@@ -14946,6 +15116,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BJ1:BR2"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="BJ3:BJ4"/>
+    <mergeCell ref="BK3:BK4"/>
+    <mergeCell ref="BL3:BN3"/>
+    <mergeCell ref="BO3:BR3"/>
+    <mergeCell ref="AW1:BH2"/>
+    <mergeCell ref="AW3:AW4"/>
+    <mergeCell ref="AX3:AX4"/>
+    <mergeCell ref="AY3:BB3"/>
+    <mergeCell ref="BC3:BH3"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="D1:P2"/>
     <mergeCell ref="R1:AA2"/>
@@ -14962,22 +15148,6 @@
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AH3:AK3"/>
     <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="BJ1:BR2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="BJ3:BJ4"/>
-    <mergeCell ref="BK3:BK4"/>
-    <mergeCell ref="BL3:BN3"/>
-    <mergeCell ref="BO3:BR3"/>
-    <mergeCell ref="AW1:BH2"/>
-    <mergeCell ref="AW3:AW4"/>
-    <mergeCell ref="AX3:AX4"/>
-    <mergeCell ref="AY3:BB3"/>
-    <mergeCell ref="BC3:BH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -15010,96 +15180,96 @@
       <c r="C1" s="15"/>
     </row>
     <row r="2" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="219" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="222" t="s">
+      <c r="B2" s="220" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="223" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="224"/>
-      <c r="J2" s="222" t="s">
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225"/>
+      <c r="J2" s="223" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="223"/>
-      <c r="L2" s="224"/>
-      <c r="N2" s="222" t="s">
+      <c r="K2" s="224"/>
+      <c r="L2" s="225"/>
+      <c r="N2" s="223" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="223"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="223"/>
-      <c r="T2" s="224"/>
-      <c r="V2" s="228" t="s">
+      <c r="O2" s="224"/>
+      <c r="P2" s="224"/>
+      <c r="Q2" s="224"/>
+      <c r="R2" s="224"/>
+      <c r="S2" s="224"/>
+      <c r="T2" s="225"/>
+      <c r="V2" s="229" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="229"/>
-      <c r="X2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="231"/>
     </row>
     <row r="3" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="220"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="226"/>
-      <c r="H3" s="227"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="227"/>
-      <c r="N3" s="225"/>
-      <c r="O3" s="226"/>
-      <c r="P3" s="226"/>
-      <c r="Q3" s="226"/>
-      <c r="R3" s="226"/>
-      <c r="S3" s="226"/>
-      <c r="T3" s="227"/>
-      <c r="V3" s="231"/>
-      <c r="W3" s="232"/>
-      <c r="X3" s="233"/>
+      <c r="B3" s="221"/>
+      <c r="D3" s="226"/>
+      <c r="E3" s="227"/>
+      <c r="F3" s="227"/>
+      <c r="G3" s="227"/>
+      <c r="H3" s="228"/>
+      <c r="J3" s="226"/>
+      <c r="K3" s="227"/>
+      <c r="L3" s="228"/>
+      <c r="N3" s="226"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
+      <c r="Q3" s="227"/>
+      <c r="R3" s="227"/>
+      <c r="S3" s="227"/>
+      <c r="T3" s="228"/>
+      <c r="V3" s="232"/>
+      <c r="W3" s="233"/>
+      <c r="X3" s="234"/>
     </row>
     <row r="4" spans="2:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="220"/>
-      <c r="D4" s="234" t="s">
+      <c r="B4" s="221"/>
+      <c r="D4" s="235" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="235"/>
-      <c r="F4" s="234" t="s">
+      <c r="E4" s="236"/>
+      <c r="F4" s="235" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="236"/>
-      <c r="H4" s="237"/>
-      <c r="J4" s="234" t="s">
+      <c r="G4" s="237"/>
+      <c r="H4" s="238"/>
+      <c r="J4" s="235" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="235"/>
+      <c r="K4" s="236"/>
       <c r="L4" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="N4" s="217" t="s">
+      <c r="N4" s="218" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="238"/>
-      <c r="P4" s="239"/>
-      <c r="Q4" s="240"/>
-      <c r="R4" s="234" t="s">
+      <c r="O4" s="239"/>
+      <c r="P4" s="240"/>
+      <c r="Q4" s="241"/>
+      <c r="R4" s="235" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="241"/>
-      <c r="T4" s="237"/>
-      <c r="V4" s="217" t="s">
+      <c r="S4" s="242"/>
+      <c r="T4" s="238"/>
+      <c r="V4" s="218" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="218"/>
+      <c r="W4" s="219"/>
       <c r="X4" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:27" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="221"/>
+      <c r="B5" s="222"/>
       <c r="D5" s="17" t="s">
         <v>43</v>
       </c>
@@ -16264,625 +16434,1095 @@
       <c r="B27" s="88">
         <v>46308</v>
       </c>
-      <c r="D27" s="168"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="86"/>
+      <c r="D27" s="168">
+        <v>101.79</v>
+      </c>
+      <c r="E27" s="87">
+        <v>0.5625</v>
+      </c>
+      <c r="F27" s="86">
+        <v>1164.9100000000001</v>
+      </c>
       <c r="G27" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="86"/>
+        <v>719.63000000000011</v>
+      </c>
+      <c r="H27" s="86">
+        <v>445.28</v>
+      </c>
       <c r="I27" s="88">
         <v>46308</v>
       </c>
-      <c r="J27" s="89"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="86"/>
+      <c r="J27" s="89">
+        <v>31.46</v>
+      </c>
+      <c r="K27" s="87">
+        <v>0.59375</v>
+      </c>
+      <c r="L27" s="86">
+        <v>629.46</v>
+      </c>
       <c r="M27" s="88">
-        <f t="shared" si="0"/>
         <v>46308</v>
       </c>
-      <c r="N27" s="89"/>
-      <c r="O27" s="87"/>
-      <c r="P27" s="89"/>
-      <c r="Q27" s="87"/>
+      <c r="N27" s="89">
+        <v>25.77</v>
+      </c>
+      <c r="O27" s="87">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="P27" s="89">
+        <v>9</v>
+      </c>
+      <c r="Q27" s="87">
+        <v>0.35416666666666669</v>
+      </c>
       <c r="R27" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="86"/>
-      <c r="T27" s="86"/>
+        <v>555.32000000000005</v>
+      </c>
+      <c r="S27" s="86">
+        <v>377.66</v>
+      </c>
+      <c r="T27" s="86">
+        <v>177.66</v>
+      </c>
       <c r="U27" s="88">
         <v>46308</v>
       </c>
-      <c r="V27" s="89"/>
-      <c r="W27" s="87"/>
-      <c r="X27" s="86"/>
+      <c r="V27" s="89">
+        <v>29.08</v>
+      </c>
+      <c r="W27" s="87">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="X27" s="86">
+        <v>554.66999999999996</v>
+      </c>
     </row>
     <row r="28" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="88">
         <v>46309</v>
       </c>
-      <c r="D28" s="168"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="86"/>
+      <c r="D28" s="168">
+        <v>111.51</v>
+      </c>
+      <c r="E28" s="87">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F28" s="86">
+        <v>1209.19</v>
+      </c>
       <c r="G28" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="86"/>
+        <v>758.73</v>
+      </c>
+      <c r="H28" s="86">
+        <v>450.46</v>
+      </c>
       <c r="I28" s="88">
         <v>46309</v>
       </c>
-      <c r="J28" s="89"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="86"/>
+      <c r="J28" s="89">
+        <v>32.35</v>
+      </c>
+      <c r="K28" s="87">
+        <v>0.34375</v>
+      </c>
+      <c r="L28" s="86">
+        <v>636.79999999999995</v>
+      </c>
       <c r="M28" s="88">
-        <f t="shared" si="0"/>
         <v>46309</v>
       </c>
-      <c r="N28" s="89"/>
-      <c r="O28" s="87"/>
-      <c r="P28" s="89"/>
-      <c r="Q28" s="87"/>
+      <c r="N28" s="89">
+        <v>25.19</v>
+      </c>
+      <c r="O28" s="87">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="P28" s="89">
+        <v>8.98</v>
+      </c>
+      <c r="Q28" s="87">
+        <v>0.85416666666666663</v>
+      </c>
       <c r="R28" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="86"/>
-      <c r="T28" s="86"/>
+        <v>556.35</v>
+      </c>
+      <c r="S28" s="86">
+        <v>379.67</v>
+      </c>
+      <c r="T28" s="86">
+        <v>176.68</v>
+      </c>
       <c r="U28" s="88">
         <v>46309</v>
       </c>
-      <c r="V28" s="89"/>
-      <c r="W28" s="87"/>
-      <c r="X28" s="86"/>
+      <c r="V28" s="89">
+        <v>27.47</v>
+      </c>
+      <c r="W28" s="87">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="X28" s="86">
+        <v>535.39</v>
+      </c>
     </row>
     <row r="29" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="88">
         <v>46310</v>
       </c>
-      <c r="D29" s="168"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="86"/>
+      <c r="D29" s="168">
+        <v>119.71</v>
+      </c>
+      <c r="E29" s="87">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="F29" s="86">
+        <v>1262.92</v>
+      </c>
       <c r="G29" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="86"/>
+        <v>793.76</v>
+      </c>
+      <c r="H29" s="86">
+        <v>469.16</v>
+      </c>
       <c r="I29" s="88">
         <v>46310</v>
       </c>
-      <c r="J29" s="89"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="86"/>
+      <c r="J29" s="89">
+        <v>35.24</v>
+      </c>
+      <c r="K29" s="87">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L29" s="86">
+        <v>643.33000000000004</v>
+      </c>
       <c r="M29" s="88">
-        <f t="shared" si="0"/>
         <v>46310</v>
       </c>
-      <c r="N29" s="89"/>
-      <c r="O29" s="87"/>
-      <c r="P29" s="89"/>
-      <c r="Q29" s="87"/>
+      <c r="N29" s="89">
+        <v>24</v>
+      </c>
+      <c r="O29" s="87">
+        <v>0.9375</v>
+      </c>
+      <c r="P29" s="89">
+        <v>8.73</v>
+      </c>
+      <c r="Q29" s="87">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="R29" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="86"/>
-      <c r="T29" s="86"/>
+        <v>565.71</v>
+      </c>
+      <c r="S29" s="86">
+        <v>387.69</v>
+      </c>
+      <c r="T29" s="86">
+        <v>178.02</v>
+      </c>
       <c r="U29" s="88">
         <v>46310</v>
       </c>
-      <c r="V29" s="89"/>
-      <c r="W29" s="87"/>
-      <c r="X29" s="86"/>
+      <c r="V29" s="89">
+        <v>25.64</v>
+      </c>
+      <c r="W29" s="87">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="X29" s="86">
+        <v>516.62</v>
+      </c>
     </row>
     <row r="30" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="88">
         <v>46311</v>
       </c>
-      <c r="D30" s="168"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="86"/>
+      <c r="D30" s="168">
+        <v>93</v>
+      </c>
+      <c r="E30" s="87">
+        <v>0.65625</v>
+      </c>
+      <c r="F30" s="86">
+        <v>1127</v>
+      </c>
       <c r="G30" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="86"/>
+        <v>699</v>
+      </c>
+      <c r="H30" s="86">
+        <v>428</v>
+      </c>
       <c r="I30" s="88">
         <v>46311</v>
       </c>
-      <c r="J30" s="89"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="86"/>
+      <c r="J30" s="89">
+        <v>33</v>
+      </c>
+      <c r="K30" s="87">
+        <v>0.59375</v>
+      </c>
+      <c r="L30" s="86">
+        <v>624</v>
+      </c>
       <c r="M30" s="88">
-        <f t="shared" si="0"/>
         <v>46311</v>
       </c>
-      <c r="N30" s="89"/>
-      <c r="O30" s="87"/>
-      <c r="P30" s="89"/>
-      <c r="Q30" s="87"/>
+      <c r="N30" s="89">
+        <v>27</v>
+      </c>
+      <c r="O30" s="87">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="P30" s="89">
+        <v>11</v>
+      </c>
+      <c r="Q30" s="87">
+        <v>0.69791666666666663</v>
+      </c>
       <c r="R30" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="86"/>
-      <c r="T30" s="86"/>
+        <v>573</v>
+      </c>
+      <c r="S30" s="86">
+        <v>395</v>
+      </c>
+      <c r="T30" s="86">
+        <v>178</v>
+      </c>
       <c r="U30" s="88">
         <v>46311</v>
       </c>
-      <c r="V30" s="89"/>
-      <c r="W30" s="87"/>
-      <c r="X30" s="86"/>
+      <c r="V30" s="89">
+        <v>30</v>
+      </c>
+      <c r="W30" s="87">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="X30" s="86">
+        <v>548</v>
+      </c>
     </row>
     <row r="31" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="88">
         <v>46312</v>
       </c>
-      <c r="D31" s="168"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="86"/>
+      <c r="D31" s="168">
+        <v>72</v>
+      </c>
+      <c r="E31" s="87">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="F31" s="86">
+        <v>890</v>
+      </c>
       <c r="G31" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="86"/>
+        <v>437</v>
+      </c>
+      <c r="H31" s="86">
+        <v>453</v>
+      </c>
       <c r="I31" s="88">
         <v>46312</v>
       </c>
-      <c r="J31" s="89"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="86"/>
+      <c r="J31" s="89">
+        <v>34</v>
+      </c>
+      <c r="K31" s="87">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="L31" s="86">
+        <v>635</v>
+      </c>
       <c r="M31" s="88">
-        <f t="shared" si="0"/>
         <v>46312</v>
       </c>
-      <c r="N31" s="89"/>
-      <c r="O31" s="87"/>
-      <c r="P31" s="89"/>
-      <c r="Q31" s="87"/>
+      <c r="N31" s="89">
+        <v>26</v>
+      </c>
+      <c r="O31" s="87">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="P31" s="89">
+        <v>9</v>
+      </c>
+      <c r="Q31" s="87">
+        <v>0.90625</v>
+      </c>
       <c r="R31" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="86"/>
-      <c r="T31" s="86"/>
+        <v>555</v>
+      </c>
+      <c r="S31" s="86">
+        <v>380</v>
+      </c>
+      <c r="T31" s="86">
+        <v>175</v>
+      </c>
       <c r="U31" s="88">
         <v>46312</v>
       </c>
-      <c r="V31" s="89"/>
-      <c r="W31" s="87"/>
-      <c r="X31" s="86"/>
+      <c r="V31" s="89">
+        <v>27</v>
+      </c>
+      <c r="W31" s="87">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="X31" s="86">
+        <v>487</v>
+      </c>
     </row>
     <row r="32" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="88">
         <v>46313</v>
       </c>
-      <c r="D32" s="168"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="86"/>
+      <c r="D32" s="168">
+        <v>73</v>
+      </c>
+      <c r="E32" s="87">
+        <v>0.90625</v>
+      </c>
+      <c r="F32" s="86">
+        <v>810</v>
+      </c>
       <c r="G32" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="86"/>
+        <v>380</v>
+      </c>
+      <c r="H32" s="86">
+        <v>430</v>
+      </c>
       <c r="I32" s="88">
         <v>46313</v>
       </c>
-      <c r="J32" s="89"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="86"/>
+      <c r="J32" s="89">
+        <v>32</v>
+      </c>
+      <c r="K32" s="87">
+        <v>0.1875</v>
+      </c>
+      <c r="L32" s="86">
+        <v>618</v>
+      </c>
       <c r="M32" s="88">
-        <f t="shared" si="0"/>
         <v>46313</v>
       </c>
-      <c r="N32" s="89"/>
-      <c r="O32" s="87"/>
-      <c r="P32" s="89"/>
-      <c r="Q32" s="87"/>
+      <c r="N32" s="89">
+        <v>22</v>
+      </c>
+      <c r="O32" s="87">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="P32" s="89">
+        <v>9</v>
+      </c>
+      <c r="Q32" s="87">
+        <v>0.9375</v>
+      </c>
       <c r="R32" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="86"/>
-      <c r="T32" s="86"/>
+        <v>538</v>
+      </c>
+      <c r="S32" s="86">
+        <v>365</v>
+      </c>
+      <c r="T32" s="86">
+        <v>173</v>
+      </c>
       <c r="U32" s="88">
         <v>46313</v>
       </c>
-      <c r="V32" s="89"/>
-      <c r="W32" s="87"/>
-      <c r="X32" s="86"/>
+      <c r="V32" s="89">
+        <v>27</v>
+      </c>
+      <c r="W32" s="87">
+        <v>0.90625</v>
+      </c>
+      <c r="X32" s="86">
+        <v>516</v>
+      </c>
     </row>
     <row r="33" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="88">
         <v>46314</v>
       </c>
-      <c r="D33" s="168"/>
-      <c r="E33" s="169"/>
-      <c r="F33" s="170"/>
+      <c r="D33" s="168">
+        <v>100</v>
+      </c>
+      <c r="E33" s="169">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F33" s="170">
+        <v>1192</v>
+      </c>
       <c r="G33" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="170"/>
+        <v>747</v>
+      </c>
+      <c r="H33" s="170">
+        <v>445</v>
+      </c>
       <c r="I33" s="88">
         <v>46314</v>
       </c>
-      <c r="J33" s="168"/>
-      <c r="K33" s="169"/>
-      <c r="L33" s="170"/>
+      <c r="J33" s="168">
+        <v>33</v>
+      </c>
+      <c r="K33" s="169">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="L33" s="170">
+        <v>659</v>
+      </c>
       <c r="M33" s="88">
-        <f t="shared" si="0"/>
         <v>46314</v>
       </c>
-      <c r="N33" s="168"/>
-      <c r="O33" s="169"/>
-      <c r="P33" s="168"/>
-      <c r="Q33" s="169"/>
+      <c r="N33" s="168">
+        <v>22.5</v>
+      </c>
+      <c r="O33" s="169">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="P33" s="168">
+        <v>9.6</v>
+      </c>
+      <c r="Q33" s="169">
+        <v>0.64583333333333337</v>
+      </c>
       <c r="R33" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="170"/>
-      <c r="T33" s="170"/>
+        <v>559</v>
+      </c>
+      <c r="S33" s="170">
+        <v>378</v>
+      </c>
+      <c r="T33" s="170">
+        <v>181</v>
+      </c>
       <c r="U33" s="88">
         <v>46314</v>
       </c>
-      <c r="V33" s="168"/>
-      <c r="W33" s="169"/>
-      <c r="X33" s="170"/>
+      <c r="V33" s="168">
+        <v>28</v>
+      </c>
+      <c r="W33" s="169">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="X33" s="170">
+        <v>558</v>
+      </c>
     </row>
     <row r="34" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="88">
         <v>46315</v>
       </c>
-      <c r="D34" s="168"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="86"/>
+      <c r="D34" s="168">
+        <v>102</v>
+      </c>
+      <c r="E34" s="87">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="F34" s="86">
+        <v>1129</v>
+      </c>
       <c r="G34" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="86"/>
+        <v>683</v>
+      </c>
+      <c r="H34" s="86">
+        <v>446</v>
+      </c>
       <c r="I34" s="88">
         <v>46315</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="87"/>
-      <c r="L34" s="86"/>
+      <c r="J34" s="89">
+        <v>35</v>
+      </c>
+      <c r="K34" s="87">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="L34" s="86">
+        <v>650</v>
+      </c>
       <c r="M34" s="88">
-        <f t="shared" si="0"/>
         <v>46315</v>
       </c>
-      <c r="N34" s="89"/>
-      <c r="O34" s="87"/>
-      <c r="P34" s="89"/>
-      <c r="Q34" s="87"/>
+      <c r="N34" s="89">
+        <v>24.6</v>
+      </c>
+      <c r="O34" s="87">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="P34" s="89">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="Q34" s="87">
+        <v>0.48958333333333331</v>
+      </c>
       <c r="R34" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="86"/>
-      <c r="T34" s="86"/>
+        <v>552</v>
+      </c>
+      <c r="S34" s="86">
+        <v>375</v>
+      </c>
+      <c r="T34" s="86">
+        <v>177</v>
+      </c>
       <c r="U34" s="88">
         <v>46315</v>
       </c>
-      <c r="V34" s="89"/>
-      <c r="W34" s="87"/>
-      <c r="X34" s="86"/>
+      <c r="V34" s="89">
+        <v>30</v>
+      </c>
+      <c r="W34" s="87">
+        <v>0.25</v>
+      </c>
+      <c r="X34" s="86">
+        <v>556</v>
+      </c>
     </row>
     <row r="35" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="88">
         <v>46316</v>
       </c>
-      <c r="D35" s="168"/>
-      <c r="E35" s="87"/>
-      <c r="F35" s="86"/>
+      <c r="D35" s="168">
+        <v>93.88</v>
+      </c>
+      <c r="E35" s="87">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="F35" s="86">
+        <v>1050.0999999999999</v>
+      </c>
       <c r="G35" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="86"/>
+        <v>612.71999999999991</v>
+      </c>
+      <c r="H35" s="86">
+        <v>437.38</v>
+      </c>
       <c r="I35" s="88">
         <v>46316</v>
       </c>
-      <c r="J35" s="89"/>
-      <c r="K35" s="87"/>
-      <c r="L35" s="86"/>
+      <c r="J35" s="89">
+        <v>36.58</v>
+      </c>
+      <c r="K35" s="87">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L35" s="86">
+        <v>657.27</v>
+      </c>
       <c r="M35" s="88">
-        <f t="shared" si="0"/>
         <v>46316</v>
       </c>
-      <c r="N35" s="89"/>
-      <c r="O35" s="87"/>
-      <c r="P35" s="89"/>
-      <c r="Q35" s="87"/>
+      <c r="N35" s="89">
+        <v>26.8</v>
+      </c>
+      <c r="O35" s="87">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="P35" s="89">
+        <v>9.31</v>
+      </c>
+      <c r="Q35" s="87">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="R35" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S35" s="86"/>
-      <c r="T35" s="86"/>
+        <v>561.05999999999995</v>
+      </c>
+      <c r="S35" s="86">
+        <v>381.67</v>
+      </c>
+      <c r="T35" s="86">
+        <v>179.39</v>
+      </c>
       <c r="U35" s="88">
         <v>46316</v>
       </c>
-      <c r="V35" s="89"/>
-      <c r="W35" s="87"/>
-      <c r="X35" s="86"/>
+      <c r="V35" s="89">
+        <v>26.8</v>
+      </c>
+      <c r="W35" s="87">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="X35" s="86">
+        <v>494.8</v>
+      </c>
     </row>
     <row r="36" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="88">
         <v>46317</v>
       </c>
-      <c r="D36" s="168"/>
-      <c r="E36" s="87"/>
-      <c r="F36" s="86"/>
+      <c r="D36" s="168">
+        <v>82.16</v>
+      </c>
+      <c r="E36" s="87">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F36" s="86">
+        <v>1072.02</v>
+      </c>
       <c r="G36" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="86"/>
+        <v>640.44000000000005</v>
+      </c>
+      <c r="H36" s="86">
+        <v>431.58</v>
+      </c>
       <c r="I36" s="88">
         <v>46317</v>
       </c>
-      <c r="J36" s="89"/>
-      <c r="K36" s="87"/>
-      <c r="L36" s="86"/>
+      <c r="J36" s="89">
+        <v>33.119999999999997</v>
+      </c>
+      <c r="K36" s="87">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="L36" s="86">
+        <v>627.29</v>
+      </c>
       <c r="M36" s="88">
-        <f t="shared" si="0"/>
         <v>46317</v>
       </c>
-      <c r="N36" s="89"/>
-      <c r="O36" s="87"/>
-      <c r="P36" s="89"/>
-      <c r="Q36" s="87"/>
+      <c r="N36" s="89">
+        <v>23.16</v>
+      </c>
+      <c r="O36" s="87">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="P36" s="89">
+        <v>10.31</v>
+      </c>
+      <c r="Q36" s="87">
+        <v>0.46875</v>
+      </c>
       <c r="R36" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="86"/>
-      <c r="T36" s="86"/>
+        <v>578.52</v>
+      </c>
+      <c r="S36" s="86">
+        <v>387.45</v>
+      </c>
+      <c r="T36" s="86">
+        <v>191.07</v>
+      </c>
       <c r="U36" s="88">
         <v>46317</v>
       </c>
-      <c r="V36" s="89"/>
-      <c r="W36" s="87"/>
-      <c r="X36" s="86"/>
+      <c r="V36" s="89">
+        <v>28.94</v>
+      </c>
+      <c r="W36" s="87">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="X36" s="86">
+        <v>571.84</v>
+      </c>
     </row>
     <row r="37" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="88">
         <v>46318</v>
       </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="86"/>
+      <c r="D37" s="168">
+        <v>90</v>
+      </c>
+      <c r="E37" s="87">
+        <v>0.5625</v>
+      </c>
+      <c r="F37" s="86">
+        <v>1039</v>
+      </c>
       <c r="G37" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="86"/>
+        <v>622</v>
+      </c>
+      <c r="H37" s="86">
+        <v>417</v>
+      </c>
       <c r="I37" s="88">
         <v>46318</v>
       </c>
-      <c r="J37" s="89"/>
-      <c r="K37" s="87"/>
-      <c r="L37" s="86"/>
+      <c r="J37" s="89">
+        <v>29</v>
+      </c>
+      <c r="K37" s="87">
+        <v>0.625</v>
+      </c>
+      <c r="L37" s="86">
+        <v>598</v>
+      </c>
       <c r="M37" s="88">
-        <f t="shared" si="0"/>
         <v>46318</v>
       </c>
-      <c r="N37" s="89"/>
-      <c r="O37" s="87"/>
-      <c r="P37" s="89"/>
-      <c r="Q37" s="87"/>
+      <c r="N37" s="89">
+        <v>24</v>
+      </c>
+      <c r="O37" s="87">
+        <v>0.75</v>
+      </c>
+      <c r="P37" s="89">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="87">
+        <v>0.85416666666666663</v>
+      </c>
       <c r="R37" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="86"/>
-      <c r="T37" s="86"/>
+        <v>567</v>
+      </c>
+      <c r="S37" s="86">
+        <v>380</v>
+      </c>
+      <c r="T37" s="86">
+        <v>187</v>
+      </c>
       <c r="U37" s="88">
         <v>46318</v>
       </c>
-      <c r="V37" s="89"/>
-      <c r="W37" s="87"/>
-      <c r="X37" s="86"/>
+      <c r="V37" s="89">
+        <v>30</v>
+      </c>
+      <c r="W37" s="87">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="X37" s="86">
+        <v>544</v>
+      </c>
     </row>
     <row r="38" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="88">
         <v>46319</v>
       </c>
-      <c r="D38" s="168"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="86"/>
+      <c r="D38" s="168">
+        <v>59</v>
+      </c>
+      <c r="E38" s="87">
+        <v>0.5625</v>
+      </c>
+      <c r="F38" s="86">
+        <v>919</v>
+      </c>
       <c r="G38" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="86"/>
+        <v>481</v>
+      </c>
+      <c r="H38" s="86">
+        <v>438</v>
+      </c>
       <c r="I38" s="88">
         <v>46319</v>
       </c>
-      <c r="J38" s="89"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="86"/>
+      <c r="J38" s="89">
+        <v>31</v>
+      </c>
+      <c r="K38" s="87">
+        <v>0.17708333333333334</v>
+      </c>
+      <c r="L38" s="86">
+        <v>488</v>
+      </c>
       <c r="M38" s="88">
-        <f t="shared" si="0"/>
         <v>46319</v>
       </c>
-      <c r="N38" s="89"/>
-      <c r="O38" s="87"/>
-      <c r="P38" s="89"/>
-      <c r="Q38" s="87"/>
+      <c r="N38" s="89">
+        <v>24</v>
+      </c>
+      <c r="O38" s="87">
+        <v>0.78125</v>
+      </c>
+      <c r="P38" s="89">
+        <v>9</v>
+      </c>
+      <c r="Q38" s="87">
+        <v>0.48958333333333331</v>
+      </c>
       <c r="R38" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S38" s="86"/>
-      <c r="T38" s="86"/>
+        <v>521</v>
+      </c>
+      <c r="S38" s="86">
+        <v>361</v>
+      </c>
+      <c r="T38" s="86">
+        <v>160</v>
+      </c>
       <c r="U38" s="88">
         <v>46319</v>
       </c>
-      <c r="V38" s="89"/>
-      <c r="W38" s="87"/>
-      <c r="X38" s="86"/>
+      <c r="V38" s="89">
+        <v>27</v>
+      </c>
+      <c r="W38" s="87">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="X38" s="86">
+        <v>485</v>
+      </c>
     </row>
     <row r="39" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="88">
         <v>46320</v>
       </c>
-      <c r="D39" s="168"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="86"/>
+      <c r="D39" s="168">
+        <v>56</v>
+      </c>
+      <c r="E39" s="87">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="F39" s="86">
+        <v>813</v>
+      </c>
       <c r="G39" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="86"/>
+        <v>378</v>
+      </c>
+      <c r="H39" s="86">
+        <v>435</v>
+      </c>
       <c r="I39" s="88">
         <v>46320</v>
       </c>
-      <c r="J39" s="89"/>
-      <c r="K39" s="87"/>
-      <c r="L39" s="86"/>
+      <c r="J39" s="89">
+        <v>30</v>
+      </c>
+      <c r="K39" s="87">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="L39" s="86">
+        <v>614</v>
+      </c>
       <c r="M39" s="88">
-        <f t="shared" si="0"/>
         <v>46320</v>
       </c>
-      <c r="N39" s="89"/>
-      <c r="O39" s="87"/>
-      <c r="P39" s="89"/>
-      <c r="Q39" s="87"/>
+      <c r="N39" s="89">
+        <v>23</v>
+      </c>
+      <c r="O39" s="87">
+        <v>0.4375</v>
+      </c>
+      <c r="P39" s="89">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="Q39" s="87">
+        <v>0.40625</v>
+      </c>
       <c r="R39" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S39" s="86"/>
-      <c r="T39" s="86"/>
+        <v>531</v>
+      </c>
+      <c r="S39" s="86">
+        <v>368</v>
+      </c>
+      <c r="T39" s="86">
+        <v>163</v>
+      </c>
       <c r="U39" s="88">
         <v>46320</v>
       </c>
-      <c r="V39" s="89"/>
-      <c r="W39" s="87"/>
-      <c r="X39" s="86"/>
+      <c r="V39" s="89">
+        <v>27</v>
+      </c>
+      <c r="W39" s="87">
+        <v>0.90625</v>
+      </c>
+      <c r="X39" s="86">
+        <v>488</v>
+      </c>
     </row>
     <row r="40" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="88">
         <v>46321</v>
       </c>
-      <c r="D40" s="168"/>
-      <c r="E40" s="169"/>
-      <c r="F40" s="170"/>
+      <c r="D40" s="168">
+        <v>106.24</v>
+      </c>
+      <c r="E40" s="169">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="F40" s="170">
+        <v>1209.69</v>
+      </c>
       <c r="G40" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="170"/>
+        <v>762.55000000000007</v>
+      </c>
+      <c r="H40" s="170">
+        <v>447.14</v>
+      </c>
       <c r="I40" s="88">
         <v>46321</v>
       </c>
-      <c r="J40" s="168"/>
-      <c r="K40" s="169"/>
-      <c r="L40" s="170"/>
+      <c r="J40" s="168">
+        <v>31.46</v>
+      </c>
+      <c r="K40" s="169">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="L40" s="170">
+        <v>636.42999999999995</v>
+      </c>
       <c r="M40" s="88">
-        <f t="shared" si="0"/>
         <v>46321</v>
       </c>
-      <c r="N40" s="168"/>
-      <c r="O40" s="169"/>
-      <c r="P40" s="168"/>
-      <c r="Q40" s="169"/>
+      <c r="N40" s="168">
+        <v>22.72</v>
+      </c>
+      <c r="O40" s="169" t="s">
+        <v>69</v>
+      </c>
+      <c r="P40" s="168">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="Q40" s="169">
+        <v>0.78125</v>
+      </c>
       <c r="R40" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="170"/>
-      <c r="T40" s="170"/>
+        <v>545</v>
+      </c>
+      <c r="S40" s="170">
+        <v>379.97</v>
+      </c>
+      <c r="T40" s="170">
+        <v>165.03</v>
+      </c>
       <c r="U40" s="88">
         <v>46321</v>
       </c>
-      <c r="V40" s="168"/>
-      <c r="W40" s="169"/>
-      <c r="X40" s="170"/>
+      <c r="V40" s="168">
+        <v>29.9</v>
+      </c>
+      <c r="W40" s="169">
+        <v>0.84375</v>
+      </c>
+      <c r="X40" s="170">
+        <v>527.46</v>
+      </c>
     </row>
     <row r="41" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="88">
         <v>46322</v>
       </c>
-      <c r="D41" s="168"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="86"/>
-      <c r="I41" s="88">
+      <c r="D41" s="180">
+        <v>89.2</v>
+      </c>
+      <c r="E41" s="179">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="F41" s="178">
+        <v>1232.44</v>
+      </c>
+      <c r="G41" s="243">
+        <f t="shared" ref="G41:G42" si="3">F41-H41</f>
+        <v>761.03</v>
+      </c>
+      <c r="H41" s="178">
+        <v>471.41</v>
+      </c>
+      <c r="I41" s="244">
         <v>46322</v>
       </c>
-      <c r="J41" s="89"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="86"/>
-      <c r="M41" s="88">
-        <f t="shared" si="0"/>
+      <c r="J41" s="180">
+        <v>35.26</v>
+      </c>
+      <c r="K41" s="179">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="L41" s="178">
+        <v>661.04</v>
+      </c>
+      <c r="M41" s="244">
+        <f t="shared" ref="M41:M42" si="4">B41</f>
         <v>46322</v>
       </c>
-      <c r="N41" s="89"/>
-      <c r="O41" s="87"/>
-      <c r="P41" s="89"/>
-      <c r="Q41" s="87"/>
+      <c r="N41" s="180">
+        <v>23.98</v>
+      </c>
+      <c r="O41" s="179">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="P41" s="180">
+        <v>10.11</v>
+      </c>
+      <c r="Q41" s="179">
+        <v>0.65625</v>
+      </c>
       <c r="R41" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="86"/>
-      <c r="T41" s="86"/>
-      <c r="U41" s="88">
+        <f t="shared" ref="R41:R42" si="5">S41+T41</f>
+        <v>550.91999999999996</v>
+      </c>
+      <c r="S41" s="178">
+        <v>381.19</v>
+      </c>
+      <c r="T41" s="178">
+        <v>169.73</v>
+      </c>
+      <c r="U41" s="244">
         <v>46322</v>
       </c>
-      <c r="V41" s="89"/>
-      <c r="W41" s="87"/>
-      <c r="X41" s="86"/>
+      <c r="V41" s="180">
+        <v>28.606000000000002</v>
+      </c>
+      <c r="W41" s="179">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="X41" s="178">
+        <v>530.62</v>
+      </c>
     </row>
     <row r="42" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="88">
         <v>46323</v>
       </c>
-      <c r="D42" s="168"/>
-      <c r="E42" s="87"/>
-      <c r="F42" s="86"/>
-      <c r="G42" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="86"/>
-      <c r="I42" s="88">
+      <c r="D42" s="180">
+        <v>125</v>
+      </c>
+      <c r="E42" s="179">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="F42" s="178">
+        <v>1220</v>
+      </c>
+      <c r="G42" s="243">
+        <f t="shared" si="3"/>
+        <v>756</v>
+      </c>
+      <c r="H42" s="178">
+        <v>464</v>
+      </c>
+      <c r="I42" s="244">
         <v>46323</v>
       </c>
-      <c r="J42" s="89"/>
-      <c r="K42" s="87"/>
-      <c r="L42" s="86"/>
-      <c r="M42" s="88">
-        <f t="shared" si="0"/>
+      <c r="J42" s="180">
+        <v>32</v>
+      </c>
+      <c r="K42" s="179">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="L42" s="178">
+        <v>626</v>
+      </c>
+      <c r="M42" s="244">
+        <f t="shared" si="4"/>
         <v>46323</v>
       </c>
-      <c r="N42" s="89"/>
-      <c r="O42" s="87"/>
-      <c r="P42" s="89"/>
-      <c r="Q42" s="87"/>
+      <c r="N42" s="180">
+        <v>28</v>
+      </c>
+      <c r="O42" s="179">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="P42" s="180">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="179">
+        <v>0.71875</v>
+      </c>
       <c r="R42" s="181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="88">
+        <f t="shared" si="5"/>
+        <v>549</v>
+      </c>
+      <c r="S42" s="178">
+        <v>384</v>
+      </c>
+      <c r="T42" s="178">
+        <v>165</v>
+      </c>
+      <c r="U42" s="244">
         <v>46323</v>
       </c>
-      <c r="V42" s="89"/>
-      <c r="W42" s="87"/>
-      <c r="X42" s="86"/>
+      <c r="V42" s="180">
+        <v>27</v>
+      </c>
+      <c r="W42" s="179">
+        <v>0.34375</v>
+      </c>
+      <c r="X42" s="178">
+        <v>551</v>
+      </c>
     </row>
     <row r="43" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="88">
@@ -17026,23 +17666,23 @@
         <v>45838</v>
       </c>
       <c r="E48" s="174">
-        <f t="shared" ref="E48:E78" si="3">F14/J48</f>
+        <f t="shared" ref="E48:E78" si="6">F14/J48</f>
         <v>0.40537780803267531</v>
       </c>
       <c r="F48" s="174">
-        <f t="shared" ref="F48:F78" si="4">L14/J48</f>
+        <f t="shared" ref="F48:F78" si="7">L14/J48</f>
         <v>0.2168141592920354</v>
       </c>
       <c r="G48" s="174">
-        <f t="shared" ref="G48:G78" si="5">S14/J48</f>
+        <f t="shared" ref="G48:G78" si="8">S14/J48</f>
         <v>0.13002042205582029</v>
       </c>
       <c r="H48" s="174">
-        <f t="shared" ref="H48:H78" si="6">T14/J48</f>
+        <f t="shared" ref="H48:H78" si="9">T14/J48</f>
         <v>5.5479918311776719E-2</v>
       </c>
       <c r="I48" s="174">
-        <f t="shared" ref="I48:I78" si="7">X14/J48</f>
+        <f t="shared" ref="I48:I78" si="10">X14/J48</f>
         <v>0.19230769230769232</v>
       </c>
       <c r="J48" s="175">
@@ -17055,27 +17695,27 @@
         <v>45839</v>
       </c>
       <c r="E49" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.40252454417952316</v>
       </c>
       <c r="F49" s="174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.22194950911640954</v>
       </c>
       <c r="G49" s="174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.13218793828892006</v>
       </c>
       <c r="H49" s="174">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.1711079943899017E-2</v>
       </c>
       <c r="I49" s="174">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.18162692847124826</v>
       </c>
       <c r="J49" s="175">
-        <f t="shared" ref="J49:J78" si="8">F15+L15+S15+T15+X15</f>
+        <f t="shared" ref="J49:J78" si="11">F15+L15+S15+T15+X15</f>
         <v>2852</v>
       </c>
     </row>
@@ -17084,27 +17724,27 @@
         <v>45840</v>
       </c>
       <c r="E50" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.39397485381801423</v>
       </c>
       <c r="F50" s="174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.22141170031972809</v>
       </c>
       <c r="G50" s="174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.13776752023504335</v>
       </c>
       <c r="H50" s="174">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.1036379871532681E-2</v>
       </c>
       <c r="I50" s="174">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.18580954575568162</v>
       </c>
       <c r="J50" s="175">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2777.36</v>
       </c>
     </row>
@@ -17113,27 +17753,27 @@
         <v>45841</v>
       </c>
       <c r="E51" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.32210475258757471</v>
       </c>
       <c r="F51" s="174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.24851815618346088</v>
       </c>
       <c r="G51" s="174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.15503251424296483</v>
       </c>
       <c r="H51" s="174">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.9167783358955598E-2</v>
       </c>
       <c r="I51" s="174">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.20517679362704394</v>
       </c>
       <c r="J51" s="175">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2432.7800000000002</v>
       </c>
     </row>
@@ -17142,27 +17782,27 @@
         <v>45842</v>
       </c>
       <c r="E52" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.3140321217244294</v>
       </c>
       <c r="F52" s="174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.25824175824175827</v>
       </c>
       <c r="G52" s="174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.15511411665257818</v>
       </c>
       <c r="H52" s="174">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.297548605240913E-2</v>
       </c>
       <c r="I52" s="174">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.20963651732882502</v>
       </c>
       <c r="J52" s="175">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2366</v>
       </c>
     </row>
@@ -17171,27 +17811,27 @@
         <v>45843</v>
       </c>
       <c r="E53" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.38661971830985914</v>
       </c>
       <c r="F53" s="174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.22323943661971832</v>
       </c>
       <c r="G53" s="174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.1334507042253521</v>
       </c>
       <c r="H53" s="174">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.7746478873239436E-2</v>
       </c>
       <c r="I53" s="174">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.198943661971831</v>
       </c>
       <c r="J53" s="175">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2840</v>
       </c>
     </row>
@@ -17200,27 +17840,27 @@
         <v>45844</v>
       </c>
       <c r="E54" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.41625041625041626</v>
       </c>
       <c r="F54" s="174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.21411921411921411</v>
       </c>
       <c r="G54" s="174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.12187812187812187</v>
       </c>
       <c r="H54" s="174">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.8275058275058272E-2</v>
       </c>
       <c r="I54" s="174">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.18947718947718947</v>
       </c>
       <c r="J54" s="175">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>3003</v>
       </c>
     </row>
@@ -17229,27 +17869,27 @@
         <v>45845</v>
       </c>
       <c r="E55" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.42092541436464087</v>
       </c>
       <c r="F55" s="174">
-        <f t="shared" ref="F55:F65" si="9">L21/J55</f>
+        <f t="shared" ref="F55:F65" si="12">L21/J55</f>
         <v>0.21788674033149172</v>
       </c>
       <c r="G55" s="174">
-        <f t="shared" ref="G55:G65" si="10">S21/J55</f>
+        <f t="shared" ref="G55:G65" si="13">S21/J55</f>
         <v>0.12603591160220995</v>
       </c>
       <c r="H55" s="174">
-        <f t="shared" ref="H55:H65" si="11">T21/J55</f>
+        <f t="shared" ref="H55:H65" si="14">T21/J55</f>
         <v>5.8701657458563539E-2</v>
       </c>
       <c r="I55" s="174">
-        <f t="shared" ref="I55:I65" si="12">X21/J55</f>
+        <f t="shared" ref="I55:I65" si="15">X21/J55</f>
         <v>0.17645027624309392</v>
       </c>
       <c r="J55" s="175">
-        <f t="shared" ref="J55:J65" si="13">F21+L21+S21+T21+X21</f>
+        <f t="shared" ref="J55:J65" si="16">F21+L21+S21+T21+X21</f>
         <v>2896</v>
       </c>
     </row>
@@ -17258,27 +17898,27 @@
         <v>45846</v>
       </c>
       <c r="E56" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.4006572617770896</v>
       </c>
       <c r="F56" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.21979302805949152</v>
       </c>
       <c r="G56" s="174">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.13640423323482453</v>
       </c>
       <c r="H56" s="174">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>6.4229579538675335E-2</v>
       </c>
       <c r="I56" s="174">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.178915897389919</v>
       </c>
       <c r="J56" s="175">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2899.91</v>
       </c>
     </row>
@@ -17287,27 +17927,27 @@
         <v>45847</v>
       </c>
       <c r="E57" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.42527932960893855</v>
       </c>
       <c r="F57" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.21892458100558659</v>
       </c>
       <c r="G57" s="174">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.13198324022346369</v>
       </c>
       <c r="H57" s="174">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>5.7960893854748605E-2</v>
       </c>
       <c r="I57" s="174">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.16585195530726257</v>
       </c>
       <c r="J57" s="175">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2864</v>
       </c>
     </row>
@@ -17316,27 +17956,27 @@
         <v>45848</v>
       </c>
       <c r="E58" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.33494558645707379</v>
       </c>
       <c r="F58" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.24465941152760984</v>
       </c>
       <c r="G58" s="174">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.15517936316001613</v>
       </c>
       <c r="H58" s="174">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>6.9729947601773479E-2</v>
       </c>
       <c r="I58" s="174">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.1954856912535268</v>
       </c>
       <c r="J58" s="175">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2481</v>
       </c>
     </row>
@@ -17345,27 +17985,27 @@
         <v>45849</v>
       </c>
       <c r="E59" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.31604538087520262</v>
       </c>
       <c r="F59" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.24513776337115073</v>
       </c>
       <c r="G59" s="174">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.15437601296596434</v>
       </c>
       <c r="H59" s="174">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>6.9692058346839544E-2</v>
       </c>
       <c r="I59" s="174">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.21474878444084278</v>
       </c>
       <c r="J59" s="175">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2468</v>
       </c>
     </row>
@@ -17374,27 +18014,27 @@
         <v>45850</v>
       </c>
       <c r="E60" s="174">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.3017999162829636</v>
       </c>
       <c r="F60" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.25198827961490161</v>
       </c>
       <c r="G60" s="174">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.15320217664294683</v>
       </c>
       <c r="H60" s="174">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>7.2833821682712435E-2</v>
       </c>
       <c r="I60" s="174">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.22017580577647552</v>
       </c>
       <c r="J60" s="175">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2389</v>
       </c>
     </row>
@@ -17402,464 +18042,464 @@
       <c r="D61" s="176">
         <v>45851</v>
       </c>
-      <c r="E61" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F61" s="174" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G61" s="174" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H61" s="174" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I61" s="174" t="e">
+      <c r="E61" s="174">
+        <f t="shared" si="6"/>
+        <v>0.40109008525113965</v>
+      </c>
+      <c r="F61" s="174">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0.21672933107466016</v>
+      </c>
+      <c r="G61" s="174">
+        <f t="shared" si="13"/>
+        <v>0.13003208968585162</v>
+      </c>
+      <c r="H61" s="174">
+        <f t="shared" si="14"/>
+        <v>6.1170102879808286E-2</v>
+      </c>
+      <c r="I61" s="174">
+        <f t="shared" si="15"/>
+        <v>0.19097839110854023</v>
       </c>
       <c r="J61" s="175">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>2904.36</v>
       </c>
     </row>
     <row r="62" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D62" s="176">
         <v>45852</v>
       </c>
-      <c r="E62" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F62" s="174" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G62" s="174" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H62" s="174" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I62" s="174" t="e">
+      <c r="E62" s="174">
+        <f t="shared" si="6"/>
+        <v>0.41160692099001617</v>
+      </c>
+      <c r="F62" s="174">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0.21676600640630692</v>
+      </c>
+      <c r="G62" s="174">
+        <f t="shared" si="13"/>
+        <v>0.12923924254441357</v>
+      </c>
+      <c r="H62" s="174">
+        <f t="shared" si="14"/>
+        <v>6.0141674013609162E-2</v>
+      </c>
+      <c r="I62" s="174">
+        <f t="shared" si="15"/>
+        <v>0.18224615604565433</v>
       </c>
       <c r="J62" s="175">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>2937.7299999999996</v>
       </c>
     </row>
     <row r="63" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D63" s="176">
         <v>45853</v>
       </c>
-      <c r="E63" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F63" s="174" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G63" s="174" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H63" s="174" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I63" s="174" t="e">
+      <c r="E63" s="174">
+        <f t="shared" si="6"/>
+        <v>0.42258196200202108</v>
+      </c>
+      <c r="F63" s="174">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0.21526276693279084</v>
+      </c>
+      <c r="G63" s="174">
+        <f t="shared" si="13"/>
+        <v>0.12972381532366542</v>
+      </c>
+      <c r="H63" s="174">
+        <f t="shared" si="14"/>
+        <v>5.956675076457716E-2</v>
+      </c>
+      <c r="I63" s="174">
+        <f t="shared" si="15"/>
+        <v>0.17286470497694559</v>
       </c>
       <c r="J63" s="175">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>2988.58</v>
       </c>
     </row>
     <row r="64" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D64" s="176">
         <v>45854</v>
       </c>
-      <c r="E64" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F64" s="174" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G64" s="174" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H64" s="174" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I64" s="174" t="e">
+      <c r="E64" s="174">
+        <f t="shared" si="6"/>
+        <v>0.39240947075208915</v>
+      </c>
+      <c r="F64" s="174">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0.21727019498607242</v>
+      </c>
+      <c r="G64" s="174">
+        <f t="shared" si="13"/>
+        <v>0.13753481894150418</v>
+      </c>
+      <c r="H64" s="174">
+        <f t="shared" si="14"/>
+        <v>6.1977715877437327E-2</v>
+      </c>
+      <c r="I64" s="174">
+        <f t="shared" si="15"/>
+        <v>0.19080779944289694</v>
       </c>
       <c r="J64" s="175">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>2872</v>
       </c>
     </row>
     <row r="65" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D65" s="176">
         <v>45855</v>
       </c>
-      <c r="E65" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F65" s="174" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G65" s="174" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H65" s="174" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I65" s="174" t="e">
+      <c r="E65" s="174">
+        <f t="shared" si="6"/>
+        <v>0.34670821971172577</v>
+      </c>
+      <c r="F65" s="174">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0.24737047136735488</v>
+      </c>
+      <c r="G65" s="174">
+        <f t="shared" si="13"/>
+        <v>0.14803272302298404</v>
+      </c>
+      <c r="H65" s="174">
+        <f t="shared" si="14"/>
+        <v>6.8172964550058432E-2</v>
+      </c>
+      <c r="I65" s="174">
+        <f t="shared" si="15"/>
+        <v>0.18971562134787689</v>
       </c>
       <c r="J65" s="175">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>2567</v>
       </c>
     </row>
     <row r="66" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D66" s="176">
         <v>45856</v>
       </c>
-      <c r="E66" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F66" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G66" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H66" s="174" t="e">
+      <c r="E66" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I66" s="174" t="e">
+        <v>0.32634971796937956</v>
+      </c>
+      <c r="F66" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.24899274778404512</v>
+      </c>
+      <c r="G66" s="174">
+        <f t="shared" si="8"/>
+        <v>0.14705882352941177</v>
+      </c>
+      <c r="H66" s="174">
+        <f t="shared" si="9"/>
+        <v>6.9701853344077358E-2</v>
+      </c>
+      <c r="I66" s="174">
+        <f t="shared" si="10"/>
+        <v>0.20789685737308622</v>
       </c>
       <c r="J66" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2482</v>
       </c>
     </row>
     <row r="67" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D67" s="176">
         <v>45857</v>
       </c>
-      <c r="E67" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F67" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G67" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H67" s="174" t="e">
+      <c r="E67" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I67" s="174" t="e">
+        <v>0.40161725067385445</v>
+      </c>
+      <c r="F67" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.22203504043126684</v>
+      </c>
+      <c r="G67" s="174">
+        <f t="shared" si="8"/>
+        <v>0.12735849056603774</v>
+      </c>
+      <c r="H67" s="174">
+        <f t="shared" si="9"/>
+        <v>6.0983827493261457E-2</v>
+      </c>
+      <c r="I67" s="174">
+        <f t="shared" si="10"/>
+        <v>0.18800539083557952</v>
       </c>
       <c r="J67" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2968</v>
       </c>
     </row>
     <row r="68" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D68" s="176">
         <v>45858</v>
       </c>
-      <c r="E68" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F68" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G68" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H68" s="174" t="e">
+      <c r="E68" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I68" s="174" t="e">
+        <v>0.39106338759958437</v>
+      </c>
+      <c r="F68" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.22514721163837895</v>
+      </c>
+      <c r="G68" s="174">
+        <f t="shared" si="8"/>
+        <v>0.12989262209906477</v>
+      </c>
+      <c r="H68" s="174">
+        <f t="shared" si="9"/>
+        <v>6.1309317630758572E-2</v>
+      </c>
+      <c r="I68" s="174">
+        <f t="shared" si="10"/>
+        <v>0.19258746103221336</v>
       </c>
       <c r="J68" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2887</v>
       </c>
     </row>
     <row r="69" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D69" s="176">
         <v>45859</v>
       </c>
-      <c r="E69" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F69" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G69" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H69" s="174" t="e">
+      <c r="E69" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I69" s="174" t="e">
+        <v>0.38002627360009839</v>
+      </c>
+      <c r="F69" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.23786293576719997</v>
+      </c>
+      <c r="G69" s="174">
+        <f t="shared" si="8"/>
+        <v>0.13812458608222986</v>
+      </c>
+      <c r="H69" s="174">
+        <f t="shared" si="9"/>
+        <v>6.4920401124770641E-2</v>
+      </c>
+      <c r="I69" s="174">
+        <f t="shared" si="10"/>
+        <v>0.17906580342570108</v>
       </c>
       <c r="J69" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2763.23</v>
       </c>
     </row>
     <row r="70" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D70" s="176">
         <v>45860</v>
       </c>
-      <c r="E70" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F70" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G70" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H70" s="174" t="e">
+      <c r="E70" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I70" s="174" t="e">
+        <v>0.37619092737053761</v>
+      </c>
+      <c r="F70" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.22012724280355267</v>
+      </c>
+      <c r="G70" s="174">
+        <f t="shared" si="8"/>
+        <v>0.13596311151817578</v>
+      </c>
+      <c r="H70" s="174">
+        <f t="shared" si="9"/>
+        <v>6.7049868932192142E-2</v>
+      </c>
+      <c r="I70" s="174">
+        <f t="shared" si="10"/>
+        <v>0.20066884937554175</v>
       </c>
       <c r="J70" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2849.67</v>
       </c>
     </row>
     <row r="71" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D71" s="176">
         <v>45861</v>
       </c>
-      <c r="E71" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F71" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G71" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H71" s="174" t="e">
+      <c r="E71" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I71" s="174" t="e">
+        <v>0.37809315866084425</v>
+      </c>
+      <c r="F71" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.21761280931586607</v>
+      </c>
+      <c r="G71" s="174">
+        <f t="shared" si="8"/>
+        <v>0.13828238719068414</v>
+      </c>
+      <c r="H71" s="174">
+        <f t="shared" si="9"/>
+        <v>6.8049490538573509E-2</v>
+      </c>
+      <c r="I71" s="174">
+        <f t="shared" si="10"/>
+        <v>0.19796215429403202</v>
       </c>
       <c r="J71" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2748</v>
       </c>
     </row>
     <row r="72" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D72" s="176">
         <v>45862</v>
       </c>
-      <c r="E72" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F72" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G72" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H72" s="174" t="e">
+      <c r="E72" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I72" s="174" t="e">
+        <v>0.38085370907583921</v>
+      </c>
+      <c r="F72" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.20223787815996686</v>
+      </c>
+      <c r="G72" s="174">
+        <f t="shared" si="8"/>
+        <v>0.14960629921259844</v>
+      </c>
+      <c r="H72" s="174">
+        <f t="shared" si="9"/>
+        <v>6.6307501036054706E-2</v>
+      </c>
+      <c r="I72" s="174">
+        <f t="shared" si="10"/>
+        <v>0.20099461251554082</v>
       </c>
       <c r="J72" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2413</v>
       </c>
     </row>
     <row r="73" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D73" s="176">
         <v>45863</v>
       </c>
-      <c r="E73" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F73" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G73" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H73" s="174" t="e">
+      <c r="E73" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I73" s="174" t="e">
+        <v>0.33237939493049878</v>
+      </c>
+      <c r="F73" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.25102207686017991</v>
+      </c>
+      <c r="G73" s="174">
+        <f t="shared" si="8"/>
+        <v>0.15044971381847916</v>
+      </c>
+      <c r="H73" s="174">
+        <f t="shared" si="9"/>
+        <v>6.6639411283728536E-2</v>
+      </c>
+      <c r="I73" s="174">
+        <f t="shared" si="10"/>
+        <v>0.19950940310711365</v>
       </c>
       <c r="J73" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2446</v>
       </c>
     </row>
     <row r="74" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D74" s="176">
         <v>45864</v>
       </c>
-      <c r="E74" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F74" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G74" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H74" s="174" t="e">
+      <c r="E74" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I74" s="174" t="e">
+        <v>0.41447895894578868</v>
+      </c>
+      <c r="F74" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.21806152306943782</v>
+      </c>
+      <c r="G74" s="174">
+        <f t="shared" si="8"/>
+        <v>0.13019002391573983</v>
+      </c>
+      <c r="H74" s="174">
+        <f t="shared" si="9"/>
+        <v>5.6544621014328882E-2</v>
+      </c>
+      <c r="I74" s="174">
+        <f t="shared" si="10"/>
+        <v>0.18072487305470467</v>
       </c>
       <c r="J74" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2918.5800000000004</v>
       </c>
     </row>
     <row r="75" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D75" s="176">
         <v>45865</v>
       </c>
-      <c r="E75" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F75" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G75" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H75" s="174" t="e">
+      <c r="E75" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I75" s="174" t="e">
+        <v>0.41426276125874784</v>
+      </c>
+      <c r="F75" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.22219682556755921</v>
+      </c>
+      <c r="G75" s="174">
+        <f t="shared" si="8"/>
+        <v>0.1281302310572702</v>
+      </c>
+      <c r="H75" s="174">
+        <f t="shared" si="9"/>
+        <v>5.7051717299379495E-2</v>
+      </c>
+      <c r="I75" s="174">
+        <f t="shared" si="10"/>
+        <v>0.17835846481704326</v>
       </c>
       <c r="J75" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2975.02</v>
       </c>
     </row>
     <row r="76" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D76" s="176">
         <v>45866</v>
       </c>
-      <c r="E76" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F76" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G76" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H76" s="174" t="e">
+      <c r="E76" s="174">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I76" s="174" t="e">
+        <v>0.41412084181941616</v>
+      </c>
+      <c r="F76" s="174">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.21249151391717583</v>
+      </c>
+      <c r="G76" s="174">
+        <f t="shared" si="8"/>
+        <v>0.13034623217922606</v>
+      </c>
+      <c r="H76" s="174">
+        <f t="shared" si="9"/>
+        <v>5.6008146639511203E-2</v>
+      </c>
+      <c r="I76" s="174">
+        <f t="shared" si="10"/>
+        <v>0.18703326544467075</v>
       </c>
       <c r="J76" s="175">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2946</v>
       </c>
     </row>
     <row r="77" spans="4:10" x14ac:dyDescent="0.25">
@@ -17867,27 +18507,27 @@
         <v>45867</v>
       </c>
       <c r="E77" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F77" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G77" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H77" s="174" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I77" s="174" t="e">
+      <c r="F77" s="174" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="G77" s="174" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H77" s="174" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I77" s="174" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="J77" s="175">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -17896,27 +18536,27 @@
         <v>45868</v>
       </c>
       <c r="E78" s="174" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F78" s="174" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G78" s="174" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H78" s="174" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I78" s="174" t="e">
+      <c r="F78" s="174" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="G78" s="174" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H78" s="174" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I78" s="174" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="J78" s="175">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -17925,27 +18565,27 @@
         <v>45869</v>
       </c>
       <c r="E79" s="174" t="e">
-        <f t="shared" ref="E79" si="14">F45/J79</f>
+        <f t="shared" ref="E79" si="17">F45/J79</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F79" s="174" t="e">
-        <f t="shared" ref="F79" si="15">L45/J79</f>
+        <f t="shared" ref="F79" si="18">L45/J79</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G79" s="174" t="e">
-        <f t="shared" ref="G79" si="16">S45/J79</f>
+        <f t="shared" ref="G79" si="19">S45/J79</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H79" s="174" t="e">
-        <f t="shared" ref="H79" si="17">T45/J79</f>
+        <f t="shared" ref="H79" si="20">T45/J79</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I79" s="174" t="e">
-        <f t="shared" ref="I79" si="18">X45/J79</f>
+        <f t="shared" ref="I79" si="21">X45/J79</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J79" s="175">
-        <f t="shared" ref="J79" si="19">F45+L45+S45+T45+X45</f>
+        <f t="shared" ref="J79" si="22">F45+L45+S45+T45+X45</f>
         <v>0</v>
       </c>
     </row>
@@ -17964,479 +18604,529 @@
     <mergeCell ref="R4:T4"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="L16:L19 L27:L32 L22:L25 L41:L42 L34:L39">
-    <cfRule type="cellIs" dxfId="96" priority="393" operator="equal">
+  <conditionalFormatting sqref="L16:L19 L27:L32 L22:L25 L34:L39">
+    <cfRule type="cellIs" dxfId="106" priority="403" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T16:T19 T27:T32 T22:T25 T41:T43 T34:T39">
-    <cfRule type="cellIs" dxfId="95" priority="394" operator="equal">
+  <conditionalFormatting sqref="T16:T19 T27:T32 T22:T25 T43 T34:T39">
+    <cfRule type="cellIs" dxfId="105" priority="404" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X16:X19 X27:X32 X22:X25 X41:X43 X34:X39">
-    <cfRule type="cellIs" dxfId="94" priority="395" operator="equal">
+  <conditionalFormatting sqref="X16:X19 X27:X32 X22:X25 X43 X34:X39">
+    <cfRule type="cellIs" dxfId="104" priority="405" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J16:J19 J27:J32 J41:J42 J34:J39 J23 J25">
-    <cfRule type="cellIs" dxfId="93" priority="396" operator="equal">
+  <conditionalFormatting sqref="J16:J19 J27:J32 J34:J39 J23 J25">
+    <cfRule type="cellIs" dxfId="103" priority="406" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V16:V19 V27:V32 V41:V43 V34:V39 V23">
-    <cfRule type="cellIs" dxfId="92" priority="397" operator="equal">
+  <conditionalFormatting sqref="V16:V19 V27:V32 V43 V34:V39 V23">
+    <cfRule type="cellIs" dxfId="102" priority="407" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D19">
-    <cfRule type="cellIs" dxfId="91" priority="398" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="408" operator="equal">
       <formula>MAX($D$14:$D$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S16:S19 S27:S32 S22:S25 S41:S43 S34:S39">
-    <cfRule type="cellIs" dxfId="90" priority="399" operator="equal">
+  <conditionalFormatting sqref="S16:S19 S27:S32 S22:S25 S43 S34:S39">
+    <cfRule type="cellIs" dxfId="100" priority="409" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N16:N19 N27:N32 N41:N42 N34:N39 N23:N25">
-    <cfRule type="cellIs" dxfId="89" priority="400" operator="equal">
+  <conditionalFormatting sqref="N16:N19 N27:N32 N34:N39 N23:N25">
+    <cfRule type="cellIs" dxfId="99" priority="410" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P16:P19 P27:P32 P41:P42 P39 P34:P37 P23:P25">
-    <cfRule type="cellIs" dxfId="88" priority="401" operator="equal">
+  <conditionalFormatting sqref="P16:P19 P27:P32 P39 P34:P37 P23:P25">
+    <cfRule type="cellIs" dxfId="98" priority="411" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="cellIs" dxfId="87" priority="325" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="335" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T26">
-    <cfRule type="cellIs" dxfId="86" priority="326" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="336" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X26">
-    <cfRule type="cellIs" dxfId="85" priority="327" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="337" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26">
-    <cfRule type="cellIs" dxfId="84" priority="328" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="338" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="cellIs" dxfId="83" priority="329" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="339" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S26">
-    <cfRule type="cellIs" dxfId="82" priority="331" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="341" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="cellIs" dxfId="81" priority="332" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="342" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26">
-    <cfRule type="cellIs" dxfId="80" priority="333" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="343" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40">
-    <cfRule type="cellIs" dxfId="79" priority="315" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="325" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T40">
-    <cfRule type="cellIs" dxfId="78" priority="316" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="326" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X40">
-    <cfRule type="cellIs" dxfId="77" priority="317" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="327" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J40">
-    <cfRule type="cellIs" dxfId="76" priority="318" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="328" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="cellIs" dxfId="75" priority="319" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="329" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S40">
-    <cfRule type="cellIs" dxfId="74" priority="321" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="331" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N40">
-    <cfRule type="cellIs" dxfId="73" priority="322" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="332" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P40">
-    <cfRule type="cellIs" dxfId="72" priority="323" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="333" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D45 D34:D42 D20:D32">
-    <cfRule type="cellIs" dxfId="71" priority="311" operator="equal">
+  <conditionalFormatting sqref="D45 D34:D40 D20:D32">
+    <cfRule type="cellIs" dxfId="81" priority="321" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20:L21">
-    <cfRule type="cellIs" dxfId="70" priority="302" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="312" operator="equal">
       <formula>MAX($L$14:$L$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T20:T21">
-    <cfRule type="cellIs" dxfId="69" priority="303" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="313" operator="equal">
       <formula>MAX($T$14:$T$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X20:X21">
-    <cfRule type="cellIs" dxfId="68" priority="304" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="314" operator="equal">
       <formula>MAX($X$14:$X$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J20:J21">
-    <cfRule type="cellIs" dxfId="67" priority="305" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="315" operator="equal">
       <formula>MAX($J$14:$J$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V20:V21">
-    <cfRule type="cellIs" dxfId="66" priority="306" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="316" operator="equal">
       <formula>MAX($V$14:$V$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S20:S21">
-    <cfRule type="cellIs" dxfId="65" priority="307" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="317" operator="equal">
       <formula>MAX($S$14:$S$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:N21">
-    <cfRule type="cellIs" dxfId="64" priority="308" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="318" operator="equal">
       <formula>MAX($N$14:$N$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P20:P21">
-    <cfRule type="cellIs" dxfId="63" priority="309" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="319" operator="equal">
       <formula>MAX($P$14:$P$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:E64">
-    <cfRule type="top10" dxfId="62" priority="301" rank="2"/>
+    <cfRule type="top10" dxfId="72" priority="311" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F79">
-    <cfRule type="top10" dxfId="61" priority="300" rank="2"/>
+    <cfRule type="top10" dxfId="71" priority="310" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G48:G64">
-    <cfRule type="top10" dxfId="60" priority="299" rank="2"/>
+    <cfRule type="top10" dxfId="70" priority="309" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:H64">
-    <cfRule type="top10" dxfId="59" priority="298" rank="2"/>
+    <cfRule type="top10" dxfId="69" priority="308" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48:I64">
-    <cfRule type="top10" dxfId="58" priority="297" rank="2"/>
+    <cfRule type="top10" dxfId="68" priority="307" rank="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V24">
-    <cfRule type="cellIs" dxfId="57" priority="267" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="277" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="cellIs" dxfId="56" priority="266" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="276" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="cellIs" dxfId="55" priority="245" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="255" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T45">
-    <cfRule type="cellIs" dxfId="54" priority="246" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="256" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X45">
-    <cfRule type="cellIs" dxfId="53" priority="247" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="257" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J45">
-    <cfRule type="cellIs" dxfId="52" priority="248" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="258" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V45">
-    <cfRule type="cellIs" dxfId="51" priority="249" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="259" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S45">
-    <cfRule type="cellIs" dxfId="50" priority="251" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="261" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45">
-    <cfRule type="cellIs" dxfId="49" priority="252" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="262" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P45">
-    <cfRule type="cellIs" dxfId="48" priority="253" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="263" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N43">
-    <cfRule type="cellIs" dxfId="47" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="214" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P43">
-    <cfRule type="cellIs" dxfId="46" priority="205" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="215" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L43">
-    <cfRule type="cellIs" dxfId="45" priority="200" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="210" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J43">
-    <cfRule type="cellIs" dxfId="44" priority="201" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="211" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43">
-    <cfRule type="cellIs" dxfId="43" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="208" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L33">
-    <cfRule type="cellIs" dxfId="42" priority="153" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="163" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33">
-    <cfRule type="cellIs" dxfId="41" priority="154" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="164" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X33">
-    <cfRule type="cellIs" dxfId="40" priority="155" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="165" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33">
-    <cfRule type="cellIs" dxfId="39" priority="156" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="166" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="cellIs" dxfId="38" priority="157" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="167" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33">
-    <cfRule type="cellIs" dxfId="37" priority="158" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="168" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33">
-    <cfRule type="cellIs" dxfId="36" priority="159" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="169" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P33">
-    <cfRule type="cellIs" dxfId="35" priority="160" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="170" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33">
-    <cfRule type="cellIs" dxfId="34" priority="152" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="162" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P38">
-    <cfRule type="cellIs" dxfId="33" priority="150" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="160" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D44">
-    <cfRule type="cellIs" dxfId="32" priority="110" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="120" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L44">
-    <cfRule type="cellIs" dxfId="31" priority="106" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="116" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J44">
-    <cfRule type="cellIs" dxfId="30" priority="107" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="117" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44">
-    <cfRule type="cellIs" dxfId="29" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="112" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P44">
-    <cfRule type="cellIs" dxfId="28" priority="103" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="113" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44">
-    <cfRule type="cellIs" dxfId="27" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="108" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S44">
-    <cfRule type="cellIs" dxfId="26" priority="99" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="109" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X44">
-    <cfRule type="cellIs" dxfId="25" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="104" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V44">
-    <cfRule type="cellIs" dxfId="24" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="105" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="cellIs" dxfId="23" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="82" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22">
-    <cfRule type="cellIs" dxfId="22" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="78" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P22">
-    <cfRule type="cellIs" dxfId="21" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="79" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J22">
-    <cfRule type="cellIs" dxfId="20" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="76" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="cellIs" dxfId="19" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="75" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
-    <cfRule type="cellIs" dxfId="18" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="66" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T15">
-    <cfRule type="cellIs" dxfId="17" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="67" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X15">
-    <cfRule type="cellIs" dxfId="16" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="68" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="cellIs" dxfId="15" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="69" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V15">
-    <cfRule type="cellIs" dxfId="14" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="70" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S15">
-    <cfRule type="cellIs" dxfId="13" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="71" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N15">
-    <cfRule type="cellIs" dxfId="12" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="72" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P15">
-    <cfRule type="cellIs" dxfId="11" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="73" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:G45">
-    <cfRule type="cellIs" dxfId="10" priority="25" operator="equal">
+  <conditionalFormatting sqref="G14:G40 G43:G45">
+    <cfRule type="cellIs" dxfId="20" priority="35" operator="equal">
       <formula>MAX($G$14:$G$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="26" operator="equal">
       <formula>MAX($D$14:$D$42)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="22" operator="equal">
       <formula>MAX($L$14:$L$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="23" operator="equal">
       <formula>MAX($J$14:$J$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
       <formula>MAX($N$14:$N$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P14">
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="21" operator="equal">
       <formula>MAX($P$14:$P$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T14">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>MAX($T$14:$T$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S14">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
       <formula>MAX($S$14:$S$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X14">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
       <formula>MAX($X$14:$X$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V14">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>MAX($V$14:$V$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J24">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L41:L42">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+      <formula>MAX($L$14:$L$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T41:T42">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+      <formula>MAX($T$14:$T$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X41:X42">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>MAX($X$14:$X$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41:J42">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>MAX($J$14:$J$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V41:V42">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+      <formula>MAX($V$14:$V$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S41:S42">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+      <formula>MAX($S$14:$S$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N41:N42">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+      <formula>MAX($N$14:$N$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P41:P42">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
+      <formula>MAX($P$14:$P$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41:D42">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>MAX($D$14:$D$42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G41:G42">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>MAX($N$14:$N$16)</formula>
+      <formula>MAX($G$14:$G$16)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18492,6 +19182,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -18738,15 +19437,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BCA511-7B91-4B72-B4F3-8175C2C806EF}">
   <ds:schemaRefs>
@@ -18759,6 +19449,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8AAD19-02EA-4280-B365-8810DF5CEEF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3450C23-B9A2-45D4-8942-0C308DF3F8F2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18775,12 +19473,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8AAD19-02EA-4280-B365-8810DF5CEEF3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>